--- a/hipoteca/tabla_amortizaciones.xlsx
+++ b/hipoteca/tabla_amortizaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/hipoteca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{6A36A00E-2702-4A70-A591-6BDDD99505EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{535C6F4C-DE33-4204-AB34-E0B7590838D5}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{6A36A00E-2702-4A70-A591-6BDDD99505EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B3DD07E-2304-4F05-A681-AFDE568B93F7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>capital 
 prestado</t>
@@ -118,6 +118,21 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>parte papa</t>
+  </si>
+  <si>
+    <t>impuestos donaciones papa</t>
+  </si>
+  <si>
+    <t>ROUNDED</t>
+  </si>
+  <si>
+    <t>donacion papa liquido</t>
+  </si>
+  <si>
+    <t>donacion papa piso</t>
   </si>
 </sst>
 </file>
@@ -453,13 +468,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5808DF-2D0F-4576-99CF-A0E928AD7DF2}">
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>15</v>
       </c>
@@ -467,23 +482,35 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>58000</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>160000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>124160</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>128000</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>128000</v>
       </c>
@@ -491,41 +518,68 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
+        <v>128000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7">
         <f>100000-73570</f>
         <v>26430</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8">
         <v>-73570</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="5">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
         <f>amort1_29840!E233</f>
         <v>116259.53000000062</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>1193</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <f>SUM(B3:B8)</f>
-        <v>379279.53000000061</v>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <f>SUM(B3:B9)</f>
+        <v>507279.53000000061</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <f>ROUND(B13,-4)</f>
+        <v>510000</v>
       </c>
     </row>
   </sheetData>

--- a/hipoteca/tabla_amortizaciones.xlsx
+++ b/hipoteca/tabla_amortizaciones.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/hipoteca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{6A36A00E-2702-4A70-A591-6BDDD99505EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B3DD07E-2304-4F05-A681-AFDE568B93F7}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{6A36A00E-2702-4A70-A591-6BDDD99505EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F1D2D5-4C78-4454-A758-293A7117A1FD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pasta_total" sheetId="4" r:id="rId1"/>
     <sheet name="sin_amortizar" sheetId="1" r:id="rId2"/>
     <sheet name="amort1_29840" sheetId="3" r:id="rId3"/>
+    <sheet name="amort1_1009" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>capital 
 prestado</t>
@@ -199,10 +200,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15987,4 +15984,5864 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8295EF7-F425-45B3-8DE5-1F0A532210ED}">
+  <dimension ref="A1:H229"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>100000</v>
+      </c>
+      <c r="B2">
+        <v>2.3E-2</v>
+      </c>
+      <c r="C2">
+        <v>385.55</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>359</v>
+      </c>
+      <c r="F2">
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>359</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>56.71</v>
+      </c>
+      <c r="E5" s="5">
+        <v>56.71</v>
+      </c>
+      <c r="F5" s="5">
+        <v>100000</v>
+      </c>
+      <c r="H5">
+        <f>E5</f>
+        <v>56.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>224</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C6" s="6">
+        <v>29839.62</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3.76</v>
+      </c>
+      <c r="E6" s="6">
+        <v>29839.62</v>
+      </c>
+      <c r="F6" s="6">
+        <f>F5-E6</f>
+        <v>70160.38</v>
+      </c>
+      <c r="H6" s="3">
+        <f>D6+E6</f>
+        <v>29843.379999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>220</v>
+      </c>
+      <c r="B7" s="4">
+        <f>EDATE(B5,1)</f>
+        <v>46235</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1009.11</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E7" s="6">
+        <f>C7+D7</f>
+        <v>1009.17</v>
+      </c>
+      <c r="F7" s="6">
+        <f>F6-C7</f>
+        <v>69151.27</v>
+      </c>
+      <c r="H7" s="3">
+        <f>D7+E7</f>
+        <v>1009.2299999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>219</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C8" s="5">
+        <v>251.07</v>
+      </c>
+      <c r="D8" s="5">
+        <v>134.47</v>
+      </c>
+      <c r="E8" s="5">
+        <v>385.54</v>
+      </c>
+      <c r="F8" s="5">
+        <f>F7-C8</f>
+        <v>68900.2</v>
+      </c>
+      <c r="H8">
+        <f>D8+E8</f>
+        <v>520.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>218</v>
+      </c>
+      <c r="B9" s="2">
+        <f>EDATE(B7,1)</f>
+        <v>46266</v>
+      </c>
+      <c r="C9" s="5">
+        <f>$C$2-D9</f>
+        <v>253.49128333333337</v>
+      </c>
+      <c r="D9" s="5">
+        <f>F8*$B$2/12</f>
+        <v>132.05871666666664</v>
+      </c>
+      <c r="E9" s="5">
+        <f>$C$2</f>
+        <v>385.55</v>
+      </c>
+      <c r="F9" s="5">
+        <f>F8-C9</f>
+        <v>68646.708716666661</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" ref="A10:A72" si="0">A9-1</f>
+        <v>217</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" ref="B10:B73" si="1">EDATE(B9,1)</f>
+        <v>46296</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" ref="C10:C73" si="2">$C$2-D10</f>
+        <v>253.97714162638891</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" ref="D10:D73" si="3">F9*$B$2/12</f>
+        <v>131.5728583736111</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" ref="E10:E73" si="4">$C$2</f>
+        <v>385.55</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" ref="F10:F73" si="5">F9-C10</f>
+        <v>68392.731575040278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>216</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="1"/>
+        <v>46327</v>
+      </c>
+      <c r="C11" s="5">
+        <f t="shared" si="2"/>
+        <v>254.46393114783947</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" si="3"/>
+        <v>131.08606885216054</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="5"/>
+        <v>68138.267643892439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>215</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="1"/>
+        <v>46357</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="shared" si="2"/>
+        <v>254.9516536825395</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="3"/>
+        <v>130.59834631746051</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="5"/>
+        <v>67883.3159902099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>214</v>
+      </c>
+      <c r="B13" s="2">
+        <f t="shared" si="1"/>
+        <v>46388</v>
+      </c>
+      <c r="C13" s="5">
+        <f t="shared" si="2"/>
+        <v>255.44031101876439</v>
+      </c>
+      <c r="D13" s="5">
+        <f t="shared" si="3"/>
+        <v>130.10968898123562</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="5"/>
+        <v>67627.875679191129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>213</v>
+      </c>
+      <c r="B14" s="2">
+        <f t="shared" si="1"/>
+        <v>46419</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" si="2"/>
+        <v>255.929904948217</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="3"/>
+        <v>129.62009505178301</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="5"/>
+        <v>67371.945774242908</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>212</v>
+      </c>
+      <c r="B15" s="2">
+        <f t="shared" si="1"/>
+        <v>46447</v>
+      </c>
+      <c r="C15" s="5">
+        <f t="shared" si="2"/>
+        <v>256.42043726603447</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="3"/>
+        <v>129.12956273396557</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="5"/>
+        <v>67115.525336976876</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>211</v>
+      </c>
+      <c r="B16" s="2">
+        <f t="shared" si="1"/>
+        <v>46478</v>
+      </c>
+      <c r="C16" s="5">
+        <f t="shared" si="2"/>
+        <v>256.9119097707943</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="3"/>
+        <v>128.63809022920569</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="5"/>
+        <v>66858.613427206088</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="B17" s="2">
+        <f t="shared" si="1"/>
+        <v>46508</v>
+      </c>
+      <c r="C17" s="5">
+        <f t="shared" si="2"/>
+        <v>257.40432426452168</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="3"/>
+        <v>128.14567573547833</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="5"/>
+        <v>66601.209102941561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>209</v>
+      </c>
+      <c r="B18" s="2">
+        <f t="shared" si="1"/>
+        <v>46539</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="shared" si="2"/>
+        <v>257.89768255269536</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="3"/>
+        <v>127.65231744730465</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="5"/>
+        <v>66343.311420388869</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>208</v>
+      </c>
+      <c r="B19" s="2">
+        <f t="shared" si="1"/>
+        <v>46569</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" si="2"/>
+        <v>258.39198644425466</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="3"/>
+        <v>127.15801355574534</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="5"/>
+        <v>66084.919433944611</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>207</v>
+      </c>
+      <c r="B20" s="2">
+        <f t="shared" si="1"/>
+        <v>46600</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" si="2"/>
+        <v>258.88723775160616</v>
+      </c>
+      <c r="D20" s="5">
+        <f t="shared" si="3"/>
+        <v>126.66276224839383</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="5"/>
+        <v>65826.032196193002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>206</v>
+      </c>
+      <c r="B21" s="2">
+        <f t="shared" si="1"/>
+        <v>46631</v>
+      </c>
+      <c r="C21" s="5">
+        <f t="shared" si="2"/>
+        <v>259.38343829063007</v>
+      </c>
+      <c r="D21" s="5">
+        <f t="shared" si="3"/>
+        <v>126.16656170936993</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="5"/>
+        <v>65566.648757902367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="B22" s="2">
+        <f t="shared" si="1"/>
+        <v>46661</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="2"/>
+        <v>259.88058988068713</v>
+      </c>
+      <c r="D22" s="5">
+        <f t="shared" si="3"/>
+        <v>125.66941011931287</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F22" s="5">
+        <f t="shared" si="5"/>
+        <v>65306.768168021677</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>204</v>
+      </c>
+      <c r="B23" s="2">
+        <f t="shared" si="1"/>
+        <v>46692</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="2"/>
+        <v>260.37869434462516</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="3"/>
+        <v>125.17130565537487</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="5"/>
+        <v>65046.389473677053</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>203</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>46722</v>
+      </c>
+      <c r="C24" s="5">
+        <f t="shared" si="2"/>
+        <v>260.87775350878564</v>
+      </c>
+      <c r="D24" s="5">
+        <f t="shared" si="3"/>
+        <v>124.67224649121435</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F24" s="5">
+        <f t="shared" si="5"/>
+        <v>64785.511720168266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>202</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="1"/>
+        <v>46753</v>
+      </c>
+      <c r="C25" s="5">
+        <f t="shared" si="2"/>
+        <v>261.37776920301081</v>
+      </c>
+      <c r="D25" s="5">
+        <f t="shared" si="3"/>
+        <v>124.17223079698918</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F25" s="5">
+        <f t="shared" si="5"/>
+        <v>64524.133950965253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>201</v>
+      </c>
+      <c r="B26" s="2">
+        <f t="shared" si="1"/>
+        <v>46784</v>
+      </c>
+      <c r="C26" s="5">
+        <f t="shared" si="2"/>
+        <v>261.87874326064997</v>
+      </c>
+      <c r="D26" s="5">
+        <f t="shared" si="3"/>
+        <v>123.67125673935006</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F26" s="5">
+        <f t="shared" si="5"/>
+        <v>64262.255207704606</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="B27" s="2">
+        <f t="shared" si="1"/>
+        <v>46813</v>
+      </c>
+      <c r="C27" s="5">
+        <f t="shared" si="2"/>
+        <v>262.38067751856619</v>
+      </c>
+      <c r="D27" s="5">
+        <f t="shared" si="3"/>
+        <v>123.16932248143382</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="5"/>
+        <v>63999.87453018604</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>199</v>
+      </c>
+      <c r="B28" s="2">
+        <f t="shared" si="1"/>
+        <v>46844</v>
+      </c>
+      <c r="C28" s="5">
+        <f t="shared" si="2"/>
+        <v>262.88357381714343</v>
+      </c>
+      <c r="D28" s="5">
+        <f t="shared" si="3"/>
+        <v>122.66642618285658</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" si="5"/>
+        <v>63736.9909563689</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="B29" s="2">
+        <f t="shared" si="1"/>
+        <v>46874</v>
+      </c>
+      <c r="C29" s="5">
+        <f t="shared" si="2"/>
+        <v>263.38743400029296</v>
+      </c>
+      <c r="D29" s="5">
+        <f t="shared" si="3"/>
+        <v>122.16256599970706</v>
+      </c>
+      <c r="E29" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="5"/>
+        <v>63473.603522368605</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>197</v>
+      </c>
+      <c r="B30" s="2">
+        <f t="shared" si="1"/>
+        <v>46905</v>
+      </c>
+      <c r="C30" s="5">
+        <f t="shared" si="2"/>
+        <v>263.89225991546022</v>
+      </c>
+      <c r="D30" s="5">
+        <f t="shared" si="3"/>
+        <v>121.65774008453981</v>
+      </c>
+      <c r="E30" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="5"/>
+        <v>63209.711262453144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>196</v>
+      </c>
+      <c r="B31" s="2">
+        <f t="shared" si="1"/>
+        <v>46935</v>
+      </c>
+      <c r="C31" s="5">
+        <f t="shared" si="2"/>
+        <v>264.39805341363149</v>
+      </c>
+      <c r="D31" s="5">
+        <f t="shared" si="3"/>
+        <v>121.15194658636852</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="5"/>
+        <v>62945.313209039516</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="B32" s="2">
+        <f t="shared" si="1"/>
+        <v>46966</v>
+      </c>
+      <c r="C32" s="5">
+        <f t="shared" si="2"/>
+        <v>264.90481634934093</v>
+      </c>
+      <c r="D32" s="5">
+        <f t="shared" si="3"/>
+        <v>120.64518365065908</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F32" s="5">
+        <f t="shared" si="5"/>
+        <v>62680.408392690173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>194</v>
+      </c>
+      <c r="B33" s="2">
+        <f t="shared" si="1"/>
+        <v>46997</v>
+      </c>
+      <c r="C33" s="5">
+        <f t="shared" si="2"/>
+        <v>265.41255058067719</v>
+      </c>
+      <c r="D33" s="5">
+        <f t="shared" si="3"/>
+        <v>120.13744941932283</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F33" s="5">
+        <f t="shared" si="5"/>
+        <v>62414.995842109493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>193</v>
+      </c>
+      <c r="B34" s="2">
+        <f t="shared" si="1"/>
+        <v>47027</v>
+      </c>
+      <c r="C34" s="5">
+        <f t="shared" si="2"/>
+        <v>265.92125796929014</v>
+      </c>
+      <c r="D34" s="5">
+        <f t="shared" si="3"/>
+        <v>119.62874203070986</v>
+      </c>
+      <c r="E34" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F34" s="5">
+        <f t="shared" si="5"/>
+        <v>62149.074584140202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>192</v>
+      </c>
+      <c r="B35" s="2">
+        <f t="shared" si="1"/>
+        <v>47058</v>
+      </c>
+      <c r="C35" s="5">
+        <f t="shared" si="2"/>
+        <v>266.43094038039794</v>
+      </c>
+      <c r="D35" s="5">
+        <f t="shared" si="3"/>
+        <v>119.11905961960206</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F35" s="5">
+        <f t="shared" si="5"/>
+        <v>61882.643643759802</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>191</v>
+      </c>
+      <c r="B36" s="2">
+        <f t="shared" si="1"/>
+        <v>47088</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="2"/>
+        <v>266.94159968279371</v>
+      </c>
+      <c r="D36" s="5">
+        <f t="shared" si="3"/>
+        <v>118.60840031720629</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F36" s="5">
+        <f t="shared" si="5"/>
+        <v>61615.702044077007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="B37" s="2">
+        <f t="shared" si="1"/>
+        <v>47119</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="shared" si="2"/>
+        <v>267.45323774885242</v>
+      </c>
+      <c r="D37" s="5">
+        <f t="shared" si="3"/>
+        <v>118.0967622511476</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F37" s="5">
+        <f t="shared" si="5"/>
+        <v>61348.248806328156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>189</v>
+      </c>
+      <c r="B38" s="2">
+        <f t="shared" si="1"/>
+        <v>47150</v>
+      </c>
+      <c r="C38" s="5">
+        <f t="shared" si="2"/>
+        <v>267.96585645453769</v>
+      </c>
+      <c r="D38" s="5">
+        <f t="shared" si="3"/>
+        <v>117.58414354546231</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F38" s="5">
+        <f t="shared" si="5"/>
+        <v>61080.282949873617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>188</v>
+      </c>
+      <c r="B39" s="2">
+        <f t="shared" si="1"/>
+        <v>47178</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="shared" si="2"/>
+        <v>268.47945767940894</v>
+      </c>
+      <c r="D39" s="5">
+        <f t="shared" si="3"/>
+        <v>117.07054232059109</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F39" s="5">
+        <f t="shared" si="5"/>
+        <v>60811.803492194209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>187</v>
+      </c>
+      <c r="B40" s="2">
+        <f t="shared" si="1"/>
+        <v>47209</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" si="2"/>
+        <v>268.99404330662776</v>
+      </c>
+      <c r="D40" s="5">
+        <f t="shared" si="3"/>
+        <v>116.55595669337224</v>
+      </c>
+      <c r="E40" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F40" s="5">
+        <f t="shared" si="5"/>
+        <v>60542.809448887579</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>186</v>
+      </c>
+      <c r="B41" s="2">
+        <f t="shared" si="1"/>
+        <v>47239</v>
+      </c>
+      <c r="C41" s="5">
+        <f t="shared" si="2"/>
+        <v>269.50961522296546</v>
+      </c>
+      <c r="D41" s="5">
+        <f t="shared" si="3"/>
+        <v>116.04038477703453</v>
+      </c>
+      <c r="E41" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F41" s="5">
+        <f t="shared" si="5"/>
+        <v>60273.299833664612</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="B42" s="2">
+        <f t="shared" si="1"/>
+        <v>47270</v>
+      </c>
+      <c r="C42" s="5">
+        <f t="shared" si="2"/>
+        <v>270.02617531880952</v>
+      </c>
+      <c r="D42" s="5">
+        <f t="shared" si="3"/>
+        <v>115.5238246811905</v>
+      </c>
+      <c r="E42" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" si="5"/>
+        <v>60003.273658345803</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>184</v>
+      </c>
+      <c r="B43" s="2">
+        <f t="shared" si="1"/>
+        <v>47300</v>
+      </c>
+      <c r="C43" s="5">
+        <f t="shared" si="2"/>
+        <v>270.54372548817054</v>
+      </c>
+      <c r="D43" s="5">
+        <f t="shared" si="3"/>
+        <v>115.00627451182946</v>
+      </c>
+      <c r="E43" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F43" s="5">
+        <f t="shared" si="5"/>
+        <v>59732.729932857634</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>183</v>
+      </c>
+      <c r="B44" s="2">
+        <f t="shared" si="1"/>
+        <v>47331</v>
+      </c>
+      <c r="C44" s="5">
+        <f t="shared" si="2"/>
+        <v>271.06226762868954</v>
+      </c>
+      <c r="D44" s="5">
+        <f t="shared" si="3"/>
+        <v>114.48773237131047</v>
+      </c>
+      <c r="E44" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F44" s="5">
+        <f t="shared" si="5"/>
+        <v>59461.667665228946</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>182</v>
+      </c>
+      <c r="B45" s="2">
+        <f t="shared" si="1"/>
+        <v>47362</v>
+      </c>
+      <c r="C45" s="5">
+        <f t="shared" si="2"/>
+        <v>271.58180364164451</v>
+      </c>
+      <c r="D45" s="5">
+        <f t="shared" si="3"/>
+        <v>113.96819635835548</v>
+      </c>
+      <c r="E45" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F45" s="5">
+        <f t="shared" si="5"/>
+        <v>59190.0858615873</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>181</v>
+      </c>
+      <c r="B46" s="2">
+        <f t="shared" si="1"/>
+        <v>47392</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" si="2"/>
+        <v>272.10233543195767</v>
+      </c>
+      <c r="D46" s="5">
+        <f t="shared" si="3"/>
+        <v>113.44766456804233</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F46" s="5">
+        <f t="shared" si="5"/>
+        <v>58917.983526155345</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="B47" s="2">
+        <f t="shared" si="1"/>
+        <v>47423</v>
+      </c>
+      <c r="C47" s="5">
+        <f t="shared" si="2"/>
+        <v>272.62386490820228</v>
+      </c>
+      <c r="D47" s="5">
+        <f t="shared" si="3"/>
+        <v>112.92613509179775</v>
+      </c>
+      <c r="E47" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F47" s="5">
+        <f t="shared" si="5"/>
+        <v>58645.359661247145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>179</v>
+      </c>
+      <c r="B48" s="2">
+        <f t="shared" si="1"/>
+        <v>47453</v>
+      </c>
+      <c r="C48" s="5">
+        <f t="shared" si="2"/>
+        <v>273.14639398260965</v>
+      </c>
+      <c r="D48" s="5">
+        <f t="shared" si="3"/>
+        <v>112.40360601739036</v>
+      </c>
+      <c r="E48" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F48" s="5">
+        <f t="shared" si="5"/>
+        <v>58372.213267264538</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>178</v>
+      </c>
+      <c r="B49" s="2">
+        <f t="shared" si="1"/>
+        <v>47484</v>
+      </c>
+      <c r="C49" s="5">
+        <f t="shared" si="2"/>
+        <v>273.66992457107631</v>
+      </c>
+      <c r="D49" s="5">
+        <f t="shared" si="3"/>
+        <v>111.8800754289237</v>
+      </c>
+      <c r="E49" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F49" s="5">
+        <f t="shared" si="5"/>
+        <v>58098.543342693461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="B50" s="2">
+        <f t="shared" si="1"/>
+        <v>47515</v>
+      </c>
+      <c r="C50" s="5">
+        <f t="shared" si="2"/>
+        <v>274.19445859317091</v>
+      </c>
+      <c r="D50" s="5">
+        <f t="shared" si="3"/>
+        <v>111.35554140682912</v>
+      </c>
+      <c r="E50" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F50" s="5">
+        <f t="shared" si="5"/>
+        <v>57824.348884100291</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+      <c r="B51" s="2">
+        <f t="shared" si="1"/>
+        <v>47543</v>
+      </c>
+      <c r="C51" s="5">
+        <f t="shared" si="2"/>
+        <v>274.71999797214113</v>
+      </c>
+      <c r="D51" s="5">
+        <f t="shared" si="3"/>
+        <v>110.83000202785888</v>
+      </c>
+      <c r="E51" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F51" s="5">
+        <f t="shared" si="5"/>
+        <v>57549.62888612815</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="B52" s="2">
+        <f t="shared" si="1"/>
+        <v>47574</v>
+      </c>
+      <c r="C52" s="5">
+        <f t="shared" si="2"/>
+        <v>275.24654463492107</v>
+      </c>
+      <c r="D52" s="5">
+        <f t="shared" si="3"/>
+        <v>110.30345536507895</v>
+      </c>
+      <c r="E52" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F52" s="5">
+        <f t="shared" si="5"/>
+        <v>57274.382341493227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>174</v>
+      </c>
+      <c r="B53" s="2">
+        <f t="shared" si="1"/>
+        <v>47604</v>
+      </c>
+      <c r="C53" s="5">
+        <f t="shared" si="2"/>
+        <v>275.77410051213798</v>
+      </c>
+      <c r="D53" s="5">
+        <f t="shared" si="3"/>
+        <v>109.77589948786202</v>
+      </c>
+      <c r="E53" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F53" s="5">
+        <f t="shared" si="5"/>
+        <v>56998.608240981092</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>173</v>
+      </c>
+      <c r="B54" s="2">
+        <f t="shared" si="1"/>
+        <v>47635</v>
+      </c>
+      <c r="C54" s="5">
+        <f t="shared" si="2"/>
+        <v>276.30266753811958</v>
+      </c>
+      <c r="D54" s="5">
+        <f t="shared" si="3"/>
+        <v>109.24733246188043</v>
+      </c>
+      <c r="E54" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F54" s="5">
+        <f t="shared" si="5"/>
+        <v>56722.305573442973</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>172</v>
+      </c>
+      <c r="B55" s="2">
+        <f t="shared" si="1"/>
+        <v>47665</v>
+      </c>
+      <c r="C55" s="5">
+        <f t="shared" si="2"/>
+        <v>276.83224765090097</v>
+      </c>
+      <c r="D55" s="5">
+        <f t="shared" si="3"/>
+        <v>108.71775234909903</v>
+      </c>
+      <c r="E55" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F55" s="5">
+        <f t="shared" si="5"/>
+        <v>56445.473325792074</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="B56" s="2">
+        <f t="shared" si="1"/>
+        <v>47696</v>
+      </c>
+      <c r="C56" s="5">
+        <f t="shared" si="2"/>
+        <v>277.36284279223185</v>
+      </c>
+      <c r="D56" s="5">
+        <f t="shared" si="3"/>
+        <v>108.18715720776815</v>
+      </c>
+      <c r="E56" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F56" s="5">
+        <f t="shared" si="5"/>
+        <v>56168.110482999844</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="B57" s="2">
+        <f t="shared" si="1"/>
+        <v>47727</v>
+      </c>
+      <c r="C57" s="5">
+        <f t="shared" si="2"/>
+        <v>277.89445490758362</v>
+      </c>
+      <c r="D57" s="5">
+        <f t="shared" si="3"/>
+        <v>107.65554509241638</v>
+      </c>
+      <c r="E57" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F57" s="5">
+        <f t="shared" si="5"/>
+        <v>55890.216028092262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="B58" s="2">
+        <f t="shared" si="1"/>
+        <v>47757</v>
+      </c>
+      <c r="C58" s="5">
+        <f t="shared" si="2"/>
+        <v>278.42708594615652</v>
+      </c>
+      <c r="D58" s="5">
+        <f t="shared" si="3"/>
+        <v>107.1229140538435</v>
+      </c>
+      <c r="E58" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F58" s="5">
+        <f t="shared" si="5"/>
+        <v>55611.788942146108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>168</v>
+      </c>
+      <c r="B59" s="2">
+        <f t="shared" si="1"/>
+        <v>47788</v>
+      </c>
+      <c r="C59" s="5">
+        <f t="shared" si="2"/>
+        <v>278.96073786088664</v>
+      </c>
+      <c r="D59" s="5">
+        <f t="shared" si="3"/>
+        <v>106.58926213911337</v>
+      </c>
+      <c r="E59" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F59" s="5">
+        <f t="shared" si="5"/>
+        <v>55332.828204285222</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="B60" s="2">
+        <f t="shared" si="1"/>
+        <v>47818</v>
+      </c>
+      <c r="C60" s="5">
+        <f t="shared" si="2"/>
+        <v>279.49541260845336</v>
+      </c>
+      <c r="D60" s="5">
+        <f t="shared" si="3"/>
+        <v>106.05458739154666</v>
+      </c>
+      <c r="E60" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F60" s="5">
+        <f t="shared" si="5"/>
+        <v>55053.332791676767</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+      <c r="B61" s="2">
+        <f t="shared" si="1"/>
+        <v>47849</v>
+      </c>
+      <c r="C61" s="5">
+        <f t="shared" si="2"/>
+        <v>280.03111214928623</v>
+      </c>
+      <c r="D61" s="5">
+        <f t="shared" si="3"/>
+        <v>105.5188878507138</v>
+      </c>
+      <c r="E61" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F61" s="5">
+        <f t="shared" si="5"/>
+        <v>54773.301679527482</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="B62" s="2">
+        <f t="shared" si="1"/>
+        <v>47880</v>
+      </c>
+      <c r="C62" s="5">
+        <f t="shared" si="2"/>
+        <v>280.56783844757234</v>
+      </c>
+      <c r="D62" s="5">
+        <f t="shared" si="3"/>
+        <v>104.98216155242767</v>
+      </c>
+      <c r="E62" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F62" s="5">
+        <f t="shared" si="5"/>
+        <v>54492.733841079906</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>164</v>
+      </c>
+      <c r="B63" s="2">
+        <f t="shared" si="1"/>
+        <v>47908</v>
+      </c>
+      <c r="C63" s="5">
+        <f t="shared" si="2"/>
+        <v>281.10559347126355</v>
+      </c>
+      <c r="D63" s="5">
+        <f t="shared" si="3"/>
+        <v>104.44440652873648</v>
+      </c>
+      <c r="E63" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F63" s="5">
+        <f t="shared" si="5"/>
+        <v>54211.628247608642</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>163</v>
+      </c>
+      <c r="B64" s="2">
+        <f t="shared" si="1"/>
+        <v>47939</v>
+      </c>
+      <c r="C64" s="5">
+        <f t="shared" si="2"/>
+        <v>281.64437919208348</v>
+      </c>
+      <c r="D64" s="5">
+        <f t="shared" si="3"/>
+        <v>103.90562080791655</v>
+      </c>
+      <c r="E64" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F64" s="5">
+        <f t="shared" si="5"/>
+        <v>53929.983868416559</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>162</v>
+      </c>
+      <c r="B65" s="2">
+        <f t="shared" si="1"/>
+        <v>47969</v>
+      </c>
+      <c r="C65" s="5">
+        <f t="shared" si="2"/>
+        <v>282.18419758553495</v>
+      </c>
+      <c r="D65" s="5">
+        <f t="shared" si="3"/>
+        <v>103.36580241446507</v>
+      </c>
+      <c r="E65" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F65" s="5">
+        <f t="shared" si="5"/>
+        <v>53647.799670831024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>161</v>
+      </c>
+      <c r="B66" s="2">
+        <f t="shared" si="1"/>
+        <v>48000</v>
+      </c>
+      <c r="C66" s="5">
+        <f t="shared" si="2"/>
+        <v>282.72505063090722</v>
+      </c>
+      <c r="D66" s="5">
+        <f t="shared" si="3"/>
+        <v>102.82494936909279</v>
+      </c>
+      <c r="E66" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F66" s="5">
+        <f t="shared" si="5"/>
+        <v>53365.074620200117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="B67" s="2">
+        <f t="shared" si="1"/>
+        <v>48030</v>
+      </c>
+      <c r="C67" s="5">
+        <f t="shared" si="2"/>
+        <v>283.26694031128312</v>
+      </c>
+      <c r="D67" s="5">
+        <f t="shared" si="3"/>
+        <v>102.28305968871689</v>
+      </c>
+      <c r="E67" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F67" s="5">
+        <f t="shared" si="5"/>
+        <v>53081.807679888836</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>159</v>
+      </c>
+      <c r="B68" s="2">
+        <f t="shared" si="1"/>
+        <v>48061</v>
+      </c>
+      <c r="C68" s="5">
+        <f t="shared" si="2"/>
+        <v>283.80986861354643</v>
+      </c>
+      <c r="D68" s="5">
+        <f t="shared" si="3"/>
+        <v>101.7401313864536</v>
+      </c>
+      <c r="E68" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F68" s="5">
+        <f t="shared" si="5"/>
+        <v>52797.997811275287</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+      <c r="B69" s="2">
+        <f t="shared" si="1"/>
+        <v>48092</v>
+      </c>
+      <c r="C69" s="5">
+        <f t="shared" si="2"/>
+        <v>284.35383752838902</v>
+      </c>
+      <c r="D69" s="5">
+        <f t="shared" si="3"/>
+        <v>101.19616247161098</v>
+      </c>
+      <c r="E69" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F69" s="5">
+        <f t="shared" si="5"/>
+        <v>52513.643973746897</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>157</v>
+      </c>
+      <c r="B70" s="2">
+        <f t="shared" si="1"/>
+        <v>48122</v>
+      </c>
+      <c r="C70" s="5">
+        <f t="shared" si="2"/>
+        <v>284.89884905031846</v>
+      </c>
+      <c r="D70" s="5">
+        <f t="shared" si="3"/>
+        <v>100.65115094968155</v>
+      </c>
+      <c r="E70" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F70" s="5">
+        <f t="shared" si="5"/>
+        <v>52228.745124696579</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>156</v>
+      </c>
+      <c r="B71" s="2">
+        <f t="shared" si="1"/>
+        <v>48153</v>
+      </c>
+      <c r="C71" s="5">
+        <f t="shared" si="2"/>
+        <v>285.44490517766491</v>
+      </c>
+      <c r="D71" s="5">
+        <f t="shared" si="3"/>
+        <v>100.1050948223351</v>
+      </c>
+      <c r="E71" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F71" s="5">
+        <f t="shared" si="5"/>
+        <v>51943.300219518911</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="B72" s="2">
+        <f t="shared" si="1"/>
+        <v>48183</v>
+      </c>
+      <c r="C72" s="5">
+        <f t="shared" si="2"/>
+        <v>285.99200791258875</v>
+      </c>
+      <c r="D72" s="5">
+        <f t="shared" si="3"/>
+        <v>99.55799208741125</v>
+      </c>
+      <c r="E72" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F72" s="5">
+        <f t="shared" si="5"/>
+        <v>51657.308211606323</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" ref="A73:A136" si="6">A72-1</f>
+        <v>154</v>
+      </c>
+      <c r="B73" s="2">
+        <f t="shared" si="1"/>
+        <v>48214</v>
+      </c>
+      <c r="C73" s="5">
+        <f t="shared" si="2"/>
+        <v>286.54015926108787</v>
+      </c>
+      <c r="D73" s="5">
+        <f t="shared" si="3"/>
+        <v>99.009840738912132</v>
+      </c>
+      <c r="E73" s="5">
+        <f t="shared" si="4"/>
+        <v>385.55</v>
+      </c>
+      <c r="F73" s="5">
+        <f t="shared" si="5"/>
+        <v>51370.768052345236</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="6"/>
+        <v>153</v>
+      </c>
+      <c r="B74" s="2">
+        <f t="shared" ref="B74:B137" si="7">EDATE(B73,1)</f>
+        <v>48245</v>
+      </c>
+      <c r="C74" s="5">
+        <f t="shared" ref="C74:C137" si="8">$C$2-D74</f>
+        <v>287.08936123300498</v>
+      </c>
+      <c r="D74" s="5">
+        <f t="shared" ref="D74:D137" si="9">F73*$B$2/12</f>
+        <v>98.460638766995032</v>
+      </c>
+      <c r="E74" s="5">
+        <f t="shared" ref="E74:E137" si="10">$C$2</f>
+        <v>385.55</v>
+      </c>
+      <c r="F74" s="5">
+        <f t="shared" ref="F74:F137" si="11">F73-C74</f>
+        <v>51083.678691112233</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="6"/>
+        <v>152</v>
+      </c>
+      <c r="B75" s="2">
+        <f t="shared" si="7"/>
+        <v>48274</v>
+      </c>
+      <c r="C75" s="5">
+        <f t="shared" si="8"/>
+        <v>287.63961584203491</v>
+      </c>
+      <c r="D75" s="5">
+        <f t="shared" si="9"/>
+        <v>97.910384157965112</v>
+      </c>
+      <c r="E75" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F75" s="5">
+        <f t="shared" si="11"/>
+        <v>50796.039075270201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="6"/>
+        <v>151</v>
+      </c>
+      <c r="B76" s="2">
+        <f t="shared" si="7"/>
+        <v>48305</v>
+      </c>
+      <c r="C76" s="5">
+        <f t="shared" si="8"/>
+        <v>288.19092510573211</v>
+      </c>
+      <c r="D76" s="5">
+        <f t="shared" si="9"/>
+        <v>97.359074894267891</v>
+      </c>
+      <c r="E76" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F76" s="5">
+        <f t="shared" si="11"/>
+        <v>50507.848150164471</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="B77" s="2">
+        <f t="shared" si="7"/>
+        <v>48335</v>
+      </c>
+      <c r="C77" s="5">
+        <f t="shared" si="8"/>
+        <v>288.74329104551811</v>
+      </c>
+      <c r="D77" s="5">
+        <f t="shared" si="9"/>
+        <v>96.806708954481905</v>
+      </c>
+      <c r="E77" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F77" s="5">
+        <f t="shared" si="11"/>
+        <v>50219.104859118954</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="6"/>
+        <v>149</v>
+      </c>
+      <c r="B78" s="2">
+        <f t="shared" si="7"/>
+        <v>48366</v>
+      </c>
+      <c r="C78" s="5">
+        <f t="shared" si="8"/>
+        <v>289.29671568668869</v>
+      </c>
+      <c r="D78" s="5">
+        <f t="shared" si="9"/>
+        <v>96.253284313311326</v>
+      </c>
+      <c r="E78" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F78" s="5">
+        <f t="shared" si="11"/>
+        <v>49929.808143432267</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="6"/>
+        <v>148</v>
+      </c>
+      <c r="B79" s="2">
+        <f t="shared" si="7"/>
+        <v>48396</v>
+      </c>
+      <c r="C79" s="5">
+        <f t="shared" si="8"/>
+        <v>289.85120105842151</v>
+      </c>
+      <c r="D79" s="5">
+        <f t="shared" si="9"/>
+        <v>95.698798941578502</v>
+      </c>
+      <c r="E79" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F79" s="5">
+        <f t="shared" si="11"/>
+        <v>49639.956942373843</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="6"/>
+        <v>147</v>
+      </c>
+      <c r="B80" s="2">
+        <f t="shared" si="7"/>
+        <v>48427</v>
+      </c>
+      <c r="C80" s="5">
+        <f t="shared" si="8"/>
+        <v>290.40674919378347</v>
+      </c>
+      <c r="D80" s="5">
+        <f t="shared" si="9"/>
+        <v>95.143250806216528</v>
+      </c>
+      <c r="E80" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F80" s="5">
+        <f t="shared" si="11"/>
+        <v>49349.550193180061</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="6"/>
+        <v>146</v>
+      </c>
+      <c r="B81" s="2">
+        <f t="shared" si="7"/>
+        <v>48458</v>
+      </c>
+      <c r="C81" s="5">
+        <f t="shared" si="8"/>
+        <v>290.96336212973824</v>
+      </c>
+      <c r="D81" s="5">
+        <f t="shared" si="9"/>
+        <v>94.586637870261782</v>
+      </c>
+      <c r="E81" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F81" s="5">
+        <f t="shared" si="11"/>
+        <v>49058.586831050321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="6"/>
+        <v>145</v>
+      </c>
+      <c r="B82" s="2">
+        <f t="shared" si="7"/>
+        <v>48488</v>
+      </c>
+      <c r="C82" s="5">
+        <f t="shared" si="8"/>
+        <v>291.52104190715357</v>
+      </c>
+      <c r="D82" s="5">
+        <f t="shared" si="9"/>
+        <v>94.028958092846452</v>
+      </c>
+      <c r="E82" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F82" s="5">
+        <f t="shared" si="11"/>
+        <v>48767.065789143169</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+      <c r="B83" s="2">
+        <f t="shared" si="7"/>
+        <v>48519</v>
+      </c>
+      <c r="C83" s="5">
+        <f t="shared" si="8"/>
+        <v>292.07979057080894</v>
+      </c>
+      <c r="D83" s="5">
+        <f t="shared" si="9"/>
+        <v>93.470209429191073</v>
+      </c>
+      <c r="E83" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F83" s="5">
+        <f t="shared" si="11"/>
+        <v>48474.98599857236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="6"/>
+        <v>143</v>
+      </c>
+      <c r="B84" s="2">
+        <f t="shared" si="7"/>
+        <v>48549</v>
+      </c>
+      <c r="C84" s="5">
+        <f t="shared" si="8"/>
+        <v>292.639610169403</v>
+      </c>
+      <c r="D84" s="5">
+        <f t="shared" si="9"/>
+        <v>92.910389830597012</v>
+      </c>
+      <c r="E84" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F84" s="5">
+        <f t="shared" si="11"/>
+        <v>48182.346388402955</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="6"/>
+        <v>142</v>
+      </c>
+      <c r="B85" s="2">
+        <f t="shared" si="7"/>
+        <v>48580</v>
+      </c>
+      <c r="C85" s="5">
+        <f t="shared" si="8"/>
+        <v>293.20050275556099</v>
+      </c>
+      <c r="D85" s="5">
+        <f t="shared" si="9"/>
+        <v>92.349497244439007</v>
+      </c>
+      <c r="E85" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F85" s="5">
+        <f t="shared" si="11"/>
+        <v>47889.145885647391</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="6"/>
+        <v>141</v>
+      </c>
+      <c r="B86" s="2">
+        <f t="shared" si="7"/>
+        <v>48611</v>
+      </c>
+      <c r="C86" s="5">
+        <f t="shared" si="8"/>
+        <v>293.76247038584251</v>
+      </c>
+      <c r="D86" s="5">
+        <f t="shared" si="9"/>
+        <v>91.787529614157506</v>
+      </c>
+      <c r="E86" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F86" s="5">
+        <f t="shared" si="11"/>
+        <v>47595.383415261545</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="6"/>
+        <v>140</v>
+      </c>
+      <c r="B87" s="2">
+        <f t="shared" si="7"/>
+        <v>48639</v>
+      </c>
+      <c r="C87" s="5">
+        <f t="shared" si="8"/>
+        <v>294.32551512074872</v>
+      </c>
+      <c r="D87" s="5">
+        <f t="shared" si="9"/>
+        <v>91.224484879251293</v>
+      </c>
+      <c r="E87" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F87" s="5">
+        <f t="shared" si="11"/>
+        <v>47301.057900140797</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="6"/>
+        <v>139</v>
+      </c>
+      <c r="B88" s="2">
+        <f t="shared" si="7"/>
+        <v>48670</v>
+      </c>
+      <c r="C88" s="5">
+        <f t="shared" si="8"/>
+        <v>294.88963902473017</v>
+      </c>
+      <c r="D88" s="5">
+        <f t="shared" si="9"/>
+        <v>90.660360975269853</v>
+      </c>
+      <c r="E88" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F88" s="5">
+        <f t="shared" si="11"/>
+        <v>47006.168261116065</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="6"/>
+        <v>138</v>
+      </c>
+      <c r="B89" s="2">
+        <f t="shared" si="7"/>
+        <v>48700</v>
+      </c>
+      <c r="C89" s="5">
+        <f t="shared" si="8"/>
+        <v>295.45484416619422</v>
+      </c>
+      <c r="D89" s="5">
+        <f t="shared" si="9"/>
+        <v>90.095155833805791</v>
+      </c>
+      <c r="E89" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F89" s="5">
+        <f t="shared" si="11"/>
+        <v>46710.713416949868</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="6"/>
+        <v>137</v>
+      </c>
+      <c r="B90" s="2">
+        <f t="shared" si="7"/>
+        <v>48731</v>
+      </c>
+      <c r="C90" s="5">
+        <f t="shared" si="8"/>
+        <v>296.02113261751276</v>
+      </c>
+      <c r="D90" s="5">
+        <f t="shared" si="9"/>
+        <v>89.528867382487249</v>
+      </c>
+      <c r="E90" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F90" s="5">
+        <f t="shared" si="11"/>
+        <v>46414.692284332355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="6"/>
+        <v>136</v>
+      </c>
+      <c r="B91" s="2">
+        <f t="shared" si="7"/>
+        <v>48761</v>
+      </c>
+      <c r="C91" s="5">
+        <f t="shared" si="8"/>
+        <v>296.58850645502969</v>
+      </c>
+      <c r="D91" s="5">
+        <f t="shared" si="9"/>
+        <v>88.961493544970338</v>
+      </c>
+      <c r="E91" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F91" s="5">
+        <f t="shared" si="11"/>
+        <v>46118.103777877324</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="6"/>
+        <v>135</v>
+      </c>
+      <c r="B92" s="2">
+        <f t="shared" si="7"/>
+        <v>48792</v>
+      </c>
+      <c r="C92" s="5">
+        <f t="shared" si="8"/>
+        <v>297.15696775906849</v>
+      </c>
+      <c r="D92" s="5">
+        <f t="shared" si="9"/>
+        <v>88.393032240931532</v>
+      </c>
+      <c r="E92" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F92" s="5">
+        <f t="shared" si="11"/>
+        <v>45820.946810118257</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="6"/>
+        <v>134</v>
+      </c>
+      <c r="B93" s="2">
+        <f t="shared" si="7"/>
+        <v>48823</v>
+      </c>
+      <c r="C93" s="5">
+        <f t="shared" si="8"/>
+        <v>297.72651861394002</v>
+      </c>
+      <c r="D93" s="5">
+        <f t="shared" si="9"/>
+        <v>87.823481386059996</v>
+      </c>
+      <c r="E93" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F93" s="5">
+        <f t="shared" si="11"/>
+        <v>45523.220291504316</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="6"/>
+        <v>133</v>
+      </c>
+      <c r="B94" s="2">
+        <f t="shared" si="7"/>
+        <v>48853</v>
+      </c>
+      <c r="C94" s="5">
+        <f t="shared" si="8"/>
+        <v>298.29716110795005</v>
+      </c>
+      <c r="D94" s="5">
+        <f t="shared" si="9"/>
+        <v>87.252838892049951</v>
+      </c>
+      <c r="E94" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F94" s="5">
+        <f t="shared" si="11"/>
+        <v>45224.923130396368</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="6"/>
+        <v>132</v>
+      </c>
+      <c r="B95" s="2">
+        <f t="shared" si="7"/>
+        <v>48884</v>
+      </c>
+      <c r="C95" s="5">
+        <f t="shared" si="8"/>
+        <v>298.86889733340695</v>
+      </c>
+      <c r="D95" s="5">
+        <f t="shared" si="9"/>
+        <v>86.681102666593048</v>
+      </c>
+      <c r="E95" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F95" s="5">
+        <f t="shared" si="11"/>
+        <v>44926.054233062961</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="6"/>
+        <v>131</v>
+      </c>
+      <c r="B96" s="2">
+        <f t="shared" si="7"/>
+        <v>48914</v>
+      </c>
+      <c r="C96" s="5">
+        <f t="shared" si="8"/>
+        <v>299.44172938662933</v>
+      </c>
+      <c r="D96" s="5">
+        <f t="shared" si="9"/>
+        <v>86.108270613370678</v>
+      </c>
+      <c r="E96" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F96" s="5">
+        <f t="shared" si="11"/>
+        <v>44626.612503676333</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="6"/>
+        <v>130</v>
+      </c>
+      <c r="B97" s="2">
+        <f t="shared" si="7"/>
+        <v>48945</v>
+      </c>
+      <c r="C97" s="5">
+        <f t="shared" si="8"/>
+        <v>300.01565936795373</v>
+      </c>
+      <c r="D97" s="5">
+        <f t="shared" si="9"/>
+        <v>85.534340632046295</v>
+      </c>
+      <c r="E97" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F97" s="5">
+        <f t="shared" si="11"/>
+        <v>44326.596844308377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="6"/>
+        <v>129</v>
+      </c>
+      <c r="B98" s="2">
+        <f t="shared" si="7"/>
+        <v>48976</v>
+      </c>
+      <c r="C98" s="5">
+        <f t="shared" si="8"/>
+        <v>300.59068938174232</v>
+      </c>
+      <c r="D98" s="5">
+        <f t="shared" si="9"/>
+        <v>84.959310618257717</v>
+      </c>
+      <c r="E98" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F98" s="5">
+        <f t="shared" si="11"/>
+        <v>44026.006154926632</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="6"/>
+        <v>128</v>
+      </c>
+      <c r="B99" s="2">
+        <f t="shared" si="7"/>
+        <v>49004</v>
+      </c>
+      <c r="C99" s="5">
+        <f t="shared" si="8"/>
+        <v>301.16682153639061</v>
+      </c>
+      <c r="D99" s="5">
+        <f t="shared" si="9"/>
+        <v>84.383178463609383</v>
+      </c>
+      <c r="E99" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F99" s="5">
+        <f t="shared" si="11"/>
+        <v>43724.839333390242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="6"/>
+        <v>127</v>
+      </c>
+      <c r="B100" s="2">
+        <f t="shared" si="7"/>
+        <v>49035</v>
+      </c>
+      <c r="C100" s="5">
+        <f t="shared" si="8"/>
+        <v>301.7440579443354</v>
+      </c>
+      <c r="D100" s="5">
+        <f t="shared" si="9"/>
+        <v>83.80594205566463</v>
+      </c>
+      <c r="E100" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F100" s="5">
+        <f t="shared" si="11"/>
+        <v>43423.095275445907</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="6"/>
+        <v>126</v>
+      </c>
+      <c r="B101" s="2">
+        <f t="shared" si="7"/>
+        <v>49065</v>
+      </c>
+      <c r="C101" s="5">
+        <f t="shared" si="8"/>
+        <v>302.32240072206201</v>
+      </c>
+      <c r="D101" s="5">
+        <f t="shared" si="9"/>
+        <v>83.227599277937983</v>
+      </c>
+      <c r="E101" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F101" s="5">
+        <f t="shared" si="11"/>
+        <v>43120.772874723843</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <f t="shared" si="6"/>
+        <v>125</v>
+      </c>
+      <c r="B102" s="2">
+        <f t="shared" si="7"/>
+        <v>49096</v>
+      </c>
+      <c r="C102" s="5">
+        <f t="shared" si="8"/>
+        <v>302.90185199011262</v>
+      </c>
+      <c r="D102" s="5">
+        <f t="shared" si="9"/>
+        <v>82.648148009887365</v>
+      </c>
+      <c r="E102" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F102" s="5">
+        <f t="shared" si="11"/>
+        <v>42817.871022733729</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <f t="shared" si="6"/>
+        <v>124</v>
+      </c>
+      <c r="B103" s="2">
+        <f t="shared" si="7"/>
+        <v>49126</v>
+      </c>
+      <c r="C103" s="5">
+        <f t="shared" si="8"/>
+        <v>303.48241387309372</v>
+      </c>
+      <c r="D103" s="5">
+        <f t="shared" si="9"/>
+        <v>82.067586126906306</v>
+      </c>
+      <c r="E103" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F103" s="5">
+        <f t="shared" si="11"/>
+        <v>42514.388608860638</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <f t="shared" si="6"/>
+        <v>123</v>
+      </c>
+      <c r="B104" s="2">
+        <f t="shared" si="7"/>
+        <v>49157</v>
+      </c>
+      <c r="C104" s="5">
+        <f t="shared" si="8"/>
+        <v>304.06408849968381</v>
+      </c>
+      <c r="D104" s="5">
+        <f t="shared" si="9"/>
+        <v>81.48591150031622</v>
+      </c>
+      <c r="E104" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F104" s="5">
+        <f t="shared" si="11"/>
+        <v>42210.324520360955</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f t="shared" si="6"/>
+        <v>122</v>
+      </c>
+      <c r="B105" s="2">
+        <f t="shared" si="7"/>
+        <v>49188</v>
+      </c>
+      <c r="C105" s="5">
+        <f t="shared" si="8"/>
+        <v>304.64687800264153</v>
+      </c>
+      <c r="D105" s="5">
+        <f t="shared" si="9"/>
+        <v>80.903121997358497</v>
+      </c>
+      <c r="E105" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F105" s="5">
+        <f t="shared" si="11"/>
+        <v>41905.677642358314</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <f t="shared" si="6"/>
+        <v>121</v>
+      </c>
+      <c r="B106" s="2">
+        <f t="shared" si="7"/>
+        <v>49218</v>
+      </c>
+      <c r="C106" s="5">
+        <f t="shared" si="8"/>
+        <v>305.23078451881327</v>
+      </c>
+      <c r="D106" s="5">
+        <f t="shared" si="9"/>
+        <v>80.31921548118676</v>
+      </c>
+      <c r="E106" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F106" s="5">
+        <f t="shared" si="11"/>
+        <v>41600.446857839503</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <f t="shared" si="6"/>
+        <v>120</v>
+      </c>
+      <c r="B107" s="2">
+        <f t="shared" si="7"/>
+        <v>49249</v>
+      </c>
+      <c r="C107" s="5">
+        <f t="shared" si="8"/>
+        <v>305.81581018914096</v>
+      </c>
+      <c r="D107" s="5">
+        <f t="shared" si="9"/>
+        <v>79.73418981085905</v>
+      </c>
+      <c r="E107" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F107" s="5">
+        <f t="shared" si="11"/>
+        <v>41294.631047650364</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <f t="shared" si="6"/>
+        <v>119</v>
+      </c>
+      <c r="B108" s="2">
+        <f t="shared" si="7"/>
+        <v>49279</v>
+      </c>
+      <c r="C108" s="5">
+        <f t="shared" si="8"/>
+        <v>306.40195715867014</v>
+      </c>
+      <c r="D108" s="5">
+        <f t="shared" si="9"/>
+        <v>79.148042841329854</v>
+      </c>
+      <c r="E108" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F108" s="5">
+        <f t="shared" si="11"/>
+        <v>40988.229090491695</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <f t="shared" si="6"/>
+        <v>118</v>
+      </c>
+      <c r="B109" s="2">
+        <f t="shared" si="7"/>
+        <v>49310</v>
+      </c>
+      <c r="C109" s="5">
+        <f t="shared" si="8"/>
+        <v>306.9892275765576</v>
+      </c>
+      <c r="D109" s="5">
+        <f t="shared" si="9"/>
+        <v>78.560772423442415</v>
+      </c>
+      <c r="E109" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F109" s="5">
+        <f t="shared" si="11"/>
+        <v>40681.239862915136</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <f t="shared" si="6"/>
+        <v>117</v>
+      </c>
+      <c r="B110" s="2">
+        <f t="shared" si="7"/>
+        <v>49341</v>
+      </c>
+      <c r="C110" s="5">
+        <f t="shared" si="8"/>
+        <v>307.57762359607932</v>
+      </c>
+      <c r="D110" s="5">
+        <f t="shared" si="9"/>
+        <v>77.972376403920677</v>
+      </c>
+      <c r="E110" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F110" s="5">
+        <f t="shared" si="11"/>
+        <v>40373.662239319056</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <f t="shared" si="6"/>
+        <v>116</v>
+      </c>
+      <c r="B111" s="2">
+        <f t="shared" si="7"/>
+        <v>49369</v>
+      </c>
+      <c r="C111" s="5">
+        <f t="shared" si="8"/>
+        <v>308.16714737463849</v>
+      </c>
+      <c r="D111" s="5">
+        <f t="shared" si="9"/>
+        <v>77.382852625361522</v>
+      </c>
+      <c r="E111" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F111" s="5">
+        <f t="shared" si="11"/>
+        <v>40065.495091944416</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <f t="shared" si="6"/>
+        <v>115</v>
+      </c>
+      <c r="B112" s="2">
+        <f t="shared" si="7"/>
+        <v>49400</v>
+      </c>
+      <c r="C112" s="5">
+        <f t="shared" si="8"/>
+        <v>308.75780107377324</v>
+      </c>
+      <c r="D112" s="5">
+        <f t="shared" si="9"/>
+        <v>76.792198926226789</v>
+      </c>
+      <c r="E112" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F112" s="5">
+        <f t="shared" si="11"/>
+        <v>39756.737290870646</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <f t="shared" si="6"/>
+        <v>114</v>
+      </c>
+      <c r="B113" s="2">
+        <f t="shared" si="7"/>
+        <v>49430</v>
+      </c>
+      <c r="C113" s="5">
+        <f t="shared" si="8"/>
+        <v>309.34958685916462</v>
+      </c>
+      <c r="D113" s="5">
+        <f t="shared" si="9"/>
+        <v>76.200413140835408</v>
+      </c>
+      <c r="E113" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F113" s="5">
+        <f t="shared" si="11"/>
+        <v>39447.387704011482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <f t="shared" si="6"/>
+        <v>113</v>
+      </c>
+      <c r="B114" s="2">
+        <f t="shared" si="7"/>
+        <v>49461</v>
+      </c>
+      <c r="C114" s="5">
+        <f t="shared" si="8"/>
+        <v>309.94250690064467</v>
+      </c>
+      <c r="D114" s="5">
+        <f t="shared" si="9"/>
+        <v>75.607493099355338</v>
+      </c>
+      <c r="E114" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F114" s="5">
+        <f t="shared" si="11"/>
+        <v>39137.445197110836</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f t="shared" si="6"/>
+        <v>112</v>
+      </c>
+      <c r="B115" s="2">
+        <f t="shared" si="7"/>
+        <v>49491</v>
+      </c>
+      <c r="C115" s="5">
+        <f t="shared" si="8"/>
+        <v>310.53656337220423</v>
+      </c>
+      <c r="D115" s="5">
+        <f t="shared" si="9"/>
+        <v>75.01343662779577</v>
+      </c>
+      <c r="E115" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F115" s="5">
+        <f t="shared" si="11"/>
+        <v>38826.908633738632</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f t="shared" si="6"/>
+        <v>111</v>
+      </c>
+      <c r="B116" s="2">
+        <f t="shared" si="7"/>
+        <v>49522</v>
+      </c>
+      <c r="C116" s="5">
+        <f t="shared" si="8"/>
+        <v>311.13175845200095</v>
+      </c>
+      <c r="D116" s="5">
+        <f t="shared" si="9"/>
+        <v>74.418241547999045</v>
+      </c>
+      <c r="E116" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F116" s="5">
+        <f t="shared" si="11"/>
+        <v>38515.776875286632</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <f t="shared" si="6"/>
+        <v>110</v>
+      </c>
+      <c r="B117" s="2">
+        <f t="shared" si="7"/>
+        <v>49553</v>
+      </c>
+      <c r="C117" s="5">
+        <f t="shared" si="8"/>
+        <v>311.72809432236727</v>
+      </c>
+      <c r="D117" s="5">
+        <f t="shared" si="9"/>
+        <v>73.821905677632714</v>
+      </c>
+      <c r="E117" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F117" s="5">
+        <f t="shared" si="11"/>
+        <v>38204.048780964265</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <f t="shared" si="6"/>
+        <v>109</v>
+      </c>
+      <c r="B118" s="2">
+        <f t="shared" si="7"/>
+        <v>49583</v>
+      </c>
+      <c r="C118" s="5">
+        <f t="shared" si="8"/>
+        <v>312.32557316981848</v>
+      </c>
+      <c r="D118" s="5">
+        <f t="shared" si="9"/>
+        <v>73.224426830181514</v>
+      </c>
+      <c r="E118" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F118" s="5">
+        <f t="shared" si="11"/>
+        <v>37891.72320779445</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <f t="shared" si="6"/>
+        <v>108</v>
+      </c>
+      <c r="B119" s="2">
+        <f t="shared" si="7"/>
+        <v>49614</v>
+      </c>
+      <c r="C119" s="5">
+        <f t="shared" si="8"/>
+        <v>312.92419718506062</v>
+      </c>
+      <c r="D119" s="5">
+        <f t="shared" si="9"/>
+        <v>72.625802814939362</v>
+      </c>
+      <c r="E119" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F119" s="5">
+        <f t="shared" si="11"/>
+        <v>37578.799010609393</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <f t="shared" si="6"/>
+        <v>107</v>
+      </c>
+      <c r="B120" s="2">
+        <f t="shared" si="7"/>
+        <v>49644</v>
+      </c>
+      <c r="C120" s="5">
+        <f t="shared" si="8"/>
+        <v>313.52396856299868</v>
+      </c>
+      <c r="D120" s="5">
+        <f t="shared" si="9"/>
+        <v>72.026031437001336</v>
+      </c>
+      <c r="E120" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F120" s="5">
+        <f t="shared" si="11"/>
+        <v>37265.275042046393</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <f t="shared" si="6"/>
+        <v>106</v>
+      </c>
+      <c r="B121" s="2">
+        <f t="shared" si="7"/>
+        <v>49675</v>
+      </c>
+      <c r="C121" s="5">
+        <f t="shared" si="8"/>
+        <v>314.1248895027444</v>
+      </c>
+      <c r="D121" s="5">
+        <f t="shared" si="9"/>
+        <v>71.425110497255588</v>
+      </c>
+      <c r="E121" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F121" s="5">
+        <f t="shared" si="11"/>
+        <v>36951.150152543647</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <f t="shared" si="6"/>
+        <v>105</v>
+      </c>
+      <c r="B122" s="2">
+        <f t="shared" si="7"/>
+        <v>49706</v>
+      </c>
+      <c r="C122" s="5">
+        <f t="shared" si="8"/>
+        <v>314.72696220762469</v>
+      </c>
+      <c r="D122" s="5">
+        <f t="shared" si="9"/>
+        <v>70.823037792375331</v>
+      </c>
+      <c r="E122" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F122" s="5">
+        <f t="shared" si="11"/>
+        <v>36636.42319033602</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <f t="shared" si="6"/>
+        <v>104</v>
+      </c>
+      <c r="B123" s="2">
+        <f t="shared" si="7"/>
+        <v>49735</v>
+      </c>
+      <c r="C123" s="5">
+        <f t="shared" si="8"/>
+        <v>315.33018888518933</v>
+      </c>
+      <c r="D123" s="5">
+        <f t="shared" si="9"/>
+        <v>70.219811114810696</v>
+      </c>
+      <c r="E123" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F123" s="5">
+        <f t="shared" si="11"/>
+        <v>36321.093001450827</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <f t="shared" si="6"/>
+        <v>103</v>
+      </c>
+      <c r="B124" s="2">
+        <f t="shared" si="7"/>
+        <v>49766</v>
+      </c>
+      <c r="C124" s="5">
+        <f t="shared" si="8"/>
+        <v>315.93457174721925</v>
+      </c>
+      <c r="D124" s="5">
+        <f t="shared" si="9"/>
+        <v>69.615428252780745</v>
+      </c>
+      <c r="E124" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F124" s="5">
+        <f t="shared" si="11"/>
+        <v>36005.15842970361</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <f t="shared" si="6"/>
+        <v>102</v>
+      </c>
+      <c r="B125" s="2">
+        <f t="shared" si="7"/>
+        <v>49796</v>
+      </c>
+      <c r="C125" s="5">
+        <f t="shared" si="8"/>
+        <v>316.54011300973474</v>
+      </c>
+      <c r="D125" s="5">
+        <f t="shared" si="9"/>
+        <v>69.009886990265258</v>
+      </c>
+      <c r="E125" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F125" s="5">
+        <f t="shared" si="11"/>
+        <v>35688.618316693872</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <f t="shared" si="6"/>
+        <v>101</v>
+      </c>
+      <c r="B126" s="2">
+        <f t="shared" si="7"/>
+        <v>49827</v>
+      </c>
+      <c r="C126" s="5">
+        <f t="shared" si="8"/>
+        <v>317.14681489300341</v>
+      </c>
+      <c r="D126" s="5">
+        <f t="shared" si="9"/>
+        <v>68.403185106996588</v>
+      </c>
+      <c r="E126" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F126" s="5">
+        <f t="shared" si="11"/>
+        <v>35371.471501800872</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="B127" s="2">
+        <f t="shared" si="7"/>
+        <v>49857</v>
+      </c>
+      <c r="C127" s="5">
+        <f t="shared" si="8"/>
+        <v>317.75467962154835</v>
+      </c>
+      <c r="D127" s="5">
+        <f t="shared" si="9"/>
+        <v>67.795320378451677</v>
+      </c>
+      <c r="E127" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F127" s="5">
+        <f t="shared" si="11"/>
+        <v>35053.716822179325</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <f t="shared" si="6"/>
+        <v>99</v>
+      </c>
+      <c r="B128" s="2">
+        <f t="shared" si="7"/>
+        <v>49888</v>
+      </c>
+      <c r="C128" s="5">
+        <f t="shared" si="8"/>
+        <v>318.3637094241563</v>
+      </c>
+      <c r="D128" s="5">
+        <f t="shared" si="9"/>
+        <v>67.186290575843699</v>
+      </c>
+      <c r="E128" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F128" s="5">
+        <f t="shared" si="11"/>
+        <v>34735.353112755169</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <f t="shared" si="6"/>
+        <v>98</v>
+      </c>
+      <c r="B129" s="2">
+        <f t="shared" si="7"/>
+        <v>49919</v>
+      </c>
+      <c r="C129" s="5">
+        <f t="shared" si="8"/>
+        <v>318.97390653388595</v>
+      </c>
+      <c r="D129" s="5">
+        <f t="shared" si="9"/>
+        <v>66.576093466114074</v>
+      </c>
+      <c r="E129" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F129" s="5">
+        <f t="shared" si="11"/>
+        <v>34416.379206221281</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <f t="shared" si="6"/>
+        <v>97</v>
+      </c>
+      <c r="B130" s="2">
+        <f t="shared" si="7"/>
+        <v>49949</v>
+      </c>
+      <c r="C130" s="5">
+        <f t="shared" si="8"/>
+        <v>319.58527318807592</v>
+      </c>
+      <c r="D130" s="5">
+        <f t="shared" si="9"/>
+        <v>65.964726811924123</v>
+      </c>
+      <c r="E130" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F130" s="5">
+        <f t="shared" si="11"/>
+        <v>34096.793933033208</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <f t="shared" si="6"/>
+        <v>96</v>
+      </c>
+      <c r="B131" s="2">
+        <f t="shared" si="7"/>
+        <v>49980</v>
+      </c>
+      <c r="C131" s="5">
+        <f t="shared" si="8"/>
+        <v>320.19781162835301</v>
+      </c>
+      <c r="D131" s="5">
+        <f t="shared" si="9"/>
+        <v>65.352188371646989</v>
+      </c>
+      <c r="E131" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F131" s="5">
+        <f t="shared" si="11"/>
+        <v>33776.596121404858</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <f t="shared" si="6"/>
+        <v>95</v>
+      </c>
+      <c r="B132" s="2">
+        <f t="shared" si="7"/>
+        <v>50010</v>
+      </c>
+      <c r="C132" s="5">
+        <f t="shared" si="8"/>
+        <v>320.81152410064067</v>
+      </c>
+      <c r="D132" s="5">
+        <f t="shared" si="9"/>
+        <v>64.738475899359315</v>
+      </c>
+      <c r="E132" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F132" s="5">
+        <f t="shared" si="11"/>
+        <v>33455.78459730422</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <f t="shared" si="6"/>
+        <v>94</v>
+      </c>
+      <c r="B133" s="2">
+        <f t="shared" si="7"/>
+        <v>50041</v>
+      </c>
+      <c r="C133" s="5">
+        <f t="shared" si="8"/>
+        <v>321.42641285516692</v>
+      </c>
+      <c r="D133" s="5">
+        <f t="shared" si="9"/>
+        <v>64.123587144833081</v>
+      </c>
+      <c r="E133" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F133" s="5">
+        <f t="shared" si="11"/>
+        <v>33134.358184449055</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <f t="shared" si="6"/>
+        <v>93</v>
+      </c>
+      <c r="B134" s="2">
+        <f t="shared" si="7"/>
+        <v>50072</v>
+      </c>
+      <c r="C134" s="5">
+        <f t="shared" si="8"/>
+        <v>322.04248014647266</v>
+      </c>
+      <c r="D134" s="5">
+        <f t="shared" si="9"/>
+        <v>63.507519853527356</v>
+      </c>
+      <c r="E134" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F134" s="5">
+        <f t="shared" si="11"/>
+        <v>32812.315704302579</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f t="shared" si="6"/>
+        <v>92</v>
+      </c>
+      <c r="B135" s="2">
+        <f t="shared" si="7"/>
+        <v>50100</v>
+      </c>
+      <c r="C135" s="5">
+        <f t="shared" si="8"/>
+        <v>322.65972823342008</v>
+      </c>
+      <c r="D135" s="5">
+        <f t="shared" si="9"/>
+        <v>62.890271766579936</v>
+      </c>
+      <c r="E135" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F135" s="5">
+        <f t="shared" si="11"/>
+        <v>32489.65597606916</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f t="shared" si="6"/>
+        <v>91</v>
+      </c>
+      <c r="B136" s="2">
+        <f t="shared" si="7"/>
+        <v>50131</v>
+      </c>
+      <c r="C136" s="5">
+        <f t="shared" si="8"/>
+        <v>323.27815937920082</v>
+      </c>
+      <c r="D136" s="5">
+        <f t="shared" si="9"/>
+        <v>62.271840620799225</v>
+      </c>
+      <c r="E136" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F136" s="5">
+        <f t="shared" si="11"/>
+        <v>32166.377816689957</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f t="shared" ref="A137:A200" si="12">A136-1</f>
+        <v>90</v>
+      </c>
+      <c r="B137" s="2">
+        <f t="shared" si="7"/>
+        <v>50161</v>
+      </c>
+      <c r="C137" s="5">
+        <f t="shared" si="8"/>
+        <v>323.89777585134425</v>
+      </c>
+      <c r="D137" s="5">
+        <f t="shared" si="9"/>
+        <v>61.652224148655755</v>
+      </c>
+      <c r="E137" s="5">
+        <f t="shared" si="10"/>
+        <v>385.55</v>
+      </c>
+      <c r="F137" s="5">
+        <f t="shared" si="11"/>
+        <v>31842.480040838615</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f t="shared" si="12"/>
+        <v>89</v>
+      </c>
+      <c r="B138" s="2">
+        <f t="shared" ref="B138:B201" si="13">EDATE(B137,1)</f>
+        <v>50192</v>
+      </c>
+      <c r="C138" s="5">
+        <f t="shared" ref="C138:C201" si="14">$C$2-D138</f>
+        <v>324.51857992172597</v>
+      </c>
+      <c r="D138" s="5">
+        <f t="shared" ref="D138:D201" si="15">F137*$B$2/12</f>
+        <v>61.03142007827401</v>
+      </c>
+      <c r="E138" s="5">
+        <f t="shared" ref="E138:E201" si="16">$C$2</f>
+        <v>385.55</v>
+      </c>
+      <c r="F138" s="5">
+        <f t="shared" ref="F138:F201" si="17">F137-C138</f>
+        <v>31517.961460916889</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f t="shared" si="12"/>
+        <v>88</v>
+      </c>
+      <c r="B139" s="2">
+        <f t="shared" si="13"/>
+        <v>50222</v>
+      </c>
+      <c r="C139" s="5">
+        <f t="shared" si="14"/>
+        <v>325.14057386657601</v>
+      </c>
+      <c r="D139" s="5">
+        <f t="shared" si="15"/>
+        <v>60.409426133424034</v>
+      </c>
+      <c r="E139" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F139" s="5">
+        <f t="shared" si="17"/>
+        <v>31192.820887050315</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <f t="shared" si="12"/>
+        <v>87</v>
+      </c>
+      <c r="B140" s="2">
+        <f t="shared" si="13"/>
+        <v>50253</v>
+      </c>
+      <c r="C140" s="5">
+        <f t="shared" si="14"/>
+        <v>325.76375996648693</v>
+      </c>
+      <c r="D140" s="5">
+        <f t="shared" si="15"/>
+        <v>59.786240033513103</v>
+      </c>
+      <c r="E140" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F140" s="5">
+        <f t="shared" si="17"/>
+        <v>30867.057127083826</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <f t="shared" si="12"/>
+        <v>86</v>
+      </c>
+      <c r="B141" s="2">
+        <f t="shared" si="13"/>
+        <v>50284</v>
+      </c>
+      <c r="C141" s="5">
+        <f t="shared" si="14"/>
+        <v>326.3881405064227</v>
+      </c>
+      <c r="D141" s="5">
+        <f t="shared" si="15"/>
+        <v>59.161859493577332</v>
+      </c>
+      <c r="E141" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F141" s="5">
+        <f t="shared" si="17"/>
+        <v>30540.668986577402</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <f t="shared" si="12"/>
+        <v>85</v>
+      </c>
+      <c r="B142" s="2">
+        <f t="shared" si="13"/>
+        <v>50314</v>
+      </c>
+      <c r="C142" s="5">
+        <f t="shared" si="14"/>
+        <v>327.01371777572666</v>
+      </c>
+      <c r="D142" s="5">
+        <f t="shared" si="15"/>
+        <v>58.53628222427335</v>
+      </c>
+      <c r="E142" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F142" s="5">
+        <f t="shared" si="17"/>
+        <v>30213.655268801675</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <f t="shared" si="12"/>
+        <v>84</v>
+      </c>
+      <c r="B143" s="2">
+        <f t="shared" si="13"/>
+        <v>50345</v>
+      </c>
+      <c r="C143" s="5">
+        <f t="shared" si="14"/>
+        <v>327.64049406813012</v>
+      </c>
+      <c r="D143" s="5">
+        <f t="shared" si="15"/>
+        <v>57.90950593186988</v>
+      </c>
+      <c r="E143" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F143" s="5">
+        <f t="shared" si="17"/>
+        <v>29886.014774733543</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <f t="shared" si="12"/>
+        <v>83</v>
+      </c>
+      <c r="B144" s="2">
+        <f t="shared" si="13"/>
+        <v>50375</v>
+      </c>
+      <c r="C144" s="5">
+        <f t="shared" si="14"/>
+        <v>328.26847168176073</v>
+      </c>
+      <c r="D144" s="5">
+        <f t="shared" si="15"/>
+        <v>57.281528318239289</v>
+      </c>
+      <c r="E144" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F144" s="5">
+        <f t="shared" si="17"/>
+        <v>29557.746303051783</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <f t="shared" si="12"/>
+        <v>82</v>
+      </c>
+      <c r="B145" s="2">
+        <f t="shared" si="13"/>
+        <v>50406</v>
+      </c>
+      <c r="C145" s="5">
+        <f t="shared" si="14"/>
+        <v>328.89765291915074</v>
+      </c>
+      <c r="D145" s="5">
+        <f t="shared" si="15"/>
+        <v>56.652347080849246</v>
+      </c>
+      <c r="E145" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F145" s="5">
+        <f t="shared" si="17"/>
+        <v>29228.848650132633</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <f t="shared" si="12"/>
+        <v>81</v>
+      </c>
+      <c r="B146" s="2">
+        <f t="shared" si="13"/>
+        <v>50437</v>
+      </c>
+      <c r="C146" s="5">
+        <f t="shared" si="14"/>
+        <v>329.52804008724581</v>
+      </c>
+      <c r="D146" s="5">
+        <f t="shared" si="15"/>
+        <v>56.02195991275422</v>
+      </c>
+      <c r="E146" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F146" s="5">
+        <f t="shared" si="17"/>
+        <v>28899.320610045386</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <f t="shared" si="12"/>
+        <v>80</v>
+      </c>
+      <c r="B147" s="2">
+        <f t="shared" si="13"/>
+        <v>50465</v>
+      </c>
+      <c r="C147" s="5">
+        <f t="shared" si="14"/>
+        <v>330.15963549741303</v>
+      </c>
+      <c r="D147" s="5">
+        <f t="shared" si="15"/>
+        <v>55.390364502586984</v>
+      </c>
+      <c r="E147" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F147" s="5">
+        <f t="shared" si="17"/>
+        <v>28569.160974547973</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <f t="shared" si="12"/>
+        <v>79</v>
+      </c>
+      <c r="B148" s="2">
+        <f t="shared" si="13"/>
+        <v>50496</v>
+      </c>
+      <c r="C148" s="5">
+        <f t="shared" si="14"/>
+        <v>330.79244146544971</v>
+      </c>
+      <c r="D148" s="5">
+        <f t="shared" si="15"/>
+        <v>54.757558534550277</v>
+      </c>
+      <c r="E148" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F148" s="5">
+        <f t="shared" si="17"/>
+        <v>28238.368533082525</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <f t="shared" si="12"/>
+        <v>78</v>
+      </c>
+      <c r="B149" s="2">
+        <f t="shared" si="13"/>
+        <v>50526</v>
+      </c>
+      <c r="C149" s="5">
+        <f t="shared" si="14"/>
+        <v>331.42646031159182</v>
+      </c>
+      <c r="D149" s="5">
+        <f t="shared" si="15"/>
+        <v>54.123539688408165</v>
+      </c>
+      <c r="E149" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F149" s="5">
+        <f t="shared" si="17"/>
+        <v>27906.942072770933</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <f t="shared" si="12"/>
+        <v>77</v>
+      </c>
+      <c r="B150" s="2">
+        <f t="shared" si="13"/>
+        <v>50557</v>
+      </c>
+      <c r="C150" s="5">
+        <f t="shared" si="14"/>
+        <v>332.06169436052238</v>
+      </c>
+      <c r="D150" s="5">
+        <f t="shared" si="15"/>
+        <v>53.488305639477623</v>
+      </c>
+      <c r="E150" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F150" s="5">
+        <f t="shared" si="17"/>
+        <v>27574.880378410409</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <f t="shared" si="12"/>
+        <v>76</v>
+      </c>
+      <c r="B151" s="2">
+        <f t="shared" si="13"/>
+        <v>50587</v>
+      </c>
+      <c r="C151" s="5">
+        <f t="shared" si="14"/>
+        <v>332.69814594138006</v>
+      </c>
+      <c r="D151" s="5">
+        <f t="shared" si="15"/>
+        <v>52.851854058619949</v>
+      </c>
+      <c r="E151" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F151" s="5">
+        <f t="shared" si="17"/>
+        <v>27242.182232469029</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <f t="shared" si="12"/>
+        <v>75</v>
+      </c>
+      <c r="B152" s="2">
+        <f t="shared" si="13"/>
+        <v>50618</v>
+      </c>
+      <c r="C152" s="5">
+        <f t="shared" si="14"/>
+        <v>333.33581738776769</v>
+      </c>
+      <c r="D152" s="5">
+        <f t="shared" si="15"/>
+        <v>52.2141826122323</v>
+      </c>
+      <c r="E152" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F152" s="5">
+        <f t="shared" si="17"/>
+        <v>26908.846415081262</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <f t="shared" si="12"/>
+        <v>74</v>
+      </c>
+      <c r="B153" s="2">
+        <f t="shared" si="13"/>
+        <v>50649</v>
+      </c>
+      <c r="C153" s="5">
+        <f t="shared" si="14"/>
+        <v>333.97471103776093</v>
+      </c>
+      <c r="D153" s="5">
+        <f t="shared" si="15"/>
+        <v>51.575288962239085</v>
+      </c>
+      <c r="E153" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F153" s="5">
+        <f t="shared" si="17"/>
+        <v>26574.8717040435</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <f t="shared" si="12"/>
+        <v>73</v>
+      </c>
+      <c r="B154" s="2">
+        <f t="shared" si="13"/>
+        <v>50679</v>
+      </c>
+      <c r="C154" s="5">
+        <f t="shared" si="14"/>
+        <v>334.61482923391662</v>
+      </c>
+      <c r="D154" s="5">
+        <f t="shared" si="15"/>
+        <v>50.935170766083381</v>
+      </c>
+      <c r="E154" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F154" s="5">
+        <f t="shared" si="17"/>
+        <v>26240.256874809584</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <f t="shared" si="12"/>
+        <v>72</v>
+      </c>
+      <c r="B155" s="2">
+        <f t="shared" si="13"/>
+        <v>50710</v>
+      </c>
+      <c r="C155" s="5">
+        <f t="shared" si="14"/>
+        <v>335.25617432328164</v>
+      </c>
+      <c r="D155" s="5">
+        <f t="shared" si="15"/>
+        <v>50.29382567671837</v>
+      </c>
+      <c r="E155" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F155" s="5">
+        <f t="shared" si="17"/>
+        <v>25905.000700486304</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <f t="shared" si="12"/>
+        <v>71</v>
+      </c>
+      <c r="B156" s="2">
+        <f t="shared" si="13"/>
+        <v>50740</v>
+      </c>
+      <c r="C156" s="5">
+        <f t="shared" si="14"/>
+        <v>335.89874865740126</v>
+      </c>
+      <c r="D156" s="5">
+        <f t="shared" si="15"/>
+        <v>49.651251342598748</v>
+      </c>
+      <c r="E156" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F156" s="5">
+        <f t="shared" si="17"/>
+        <v>25569.101951828903</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <f t="shared" si="12"/>
+        <v>70</v>
+      </c>
+      <c r="B157" s="2">
+        <f t="shared" si="13"/>
+        <v>50771</v>
+      </c>
+      <c r="C157" s="5">
+        <f t="shared" si="14"/>
+        <v>336.54255459232797</v>
+      </c>
+      <c r="D157" s="5">
+        <f t="shared" si="15"/>
+        <v>49.007445407672066</v>
+      </c>
+      <c r="E157" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F157" s="5">
+        <f t="shared" si="17"/>
+        <v>25232.559397236575</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <f t="shared" si="12"/>
+        <v>69</v>
+      </c>
+      <c r="B158" s="2">
+        <f t="shared" si="13"/>
+        <v>50802</v>
+      </c>
+      <c r="C158" s="5">
+        <f t="shared" si="14"/>
+        <v>337.18759448862988</v>
+      </c>
+      <c r="D158" s="5">
+        <f t="shared" si="15"/>
+        <v>48.362405511370099</v>
+      </c>
+      <c r="E158" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F158" s="5">
+        <f t="shared" si="17"/>
+        <v>24895.371802747944</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <f t="shared" si="12"/>
+        <v>68</v>
+      </c>
+      <c r="B159" s="2">
+        <f t="shared" si="13"/>
+        <v>50830</v>
+      </c>
+      <c r="C159" s="5">
+        <f t="shared" si="14"/>
+        <v>337.83387071139975</v>
+      </c>
+      <c r="D159" s="5">
+        <f t="shared" si="15"/>
+        <v>47.716129288600229</v>
+      </c>
+      <c r="E159" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F159" s="5">
+        <f t="shared" si="17"/>
+        <v>24557.537932036546</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <f t="shared" si="12"/>
+        <v>67</v>
+      </c>
+      <c r="B160" s="2">
+        <f t="shared" si="13"/>
+        <v>50861</v>
+      </c>
+      <c r="C160" s="5">
+        <f t="shared" si="14"/>
+        <v>338.48138563026328</v>
+      </c>
+      <c r="D160" s="5">
+        <f t="shared" si="15"/>
+        <v>47.068614369736714</v>
+      </c>
+      <c r="E160" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F160" s="5">
+        <f t="shared" si="17"/>
+        <v>24219.056546406282</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <f t="shared" si="12"/>
+        <v>66</v>
+      </c>
+      <c r="B161" s="2">
+        <f t="shared" si="13"/>
+        <v>50891</v>
+      </c>
+      <c r="C161" s="5">
+        <f t="shared" si="14"/>
+        <v>339.13014161938798</v>
+      </c>
+      <c r="D161" s="5">
+        <f t="shared" si="15"/>
+        <v>46.419858380612034</v>
+      </c>
+      <c r="E161" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F161" s="5">
+        <f t="shared" si="17"/>
+        <v>23879.926404786893</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <f t="shared" si="12"/>
+        <v>65</v>
+      </c>
+      <c r="B162" s="2">
+        <f t="shared" si="13"/>
+        <v>50922</v>
+      </c>
+      <c r="C162" s="5">
+        <f t="shared" si="14"/>
+        <v>339.78014105749179</v>
+      </c>
+      <c r="D162" s="5">
+        <f t="shared" si="15"/>
+        <v>45.769858942508215</v>
+      </c>
+      <c r="E162" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F162" s="5">
+        <f t="shared" si="17"/>
+        <v>23540.146263729403</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <f t="shared" si="12"/>
+        <v>64</v>
+      </c>
+      <c r="B163" s="2">
+        <f t="shared" si="13"/>
+        <v>50952</v>
+      </c>
+      <c r="C163" s="5">
+        <f t="shared" si="14"/>
+        <v>340.43138632785201</v>
+      </c>
+      <c r="D163" s="5">
+        <f t="shared" si="15"/>
+        <v>45.118613672148022</v>
+      </c>
+      <c r="E163" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F163" s="5">
+        <f t="shared" si="17"/>
+        <v>23199.714877401551</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <f t="shared" si="12"/>
+        <v>63</v>
+      </c>
+      <c r="B164" s="2">
+        <f t="shared" si="13"/>
+        <v>50983</v>
+      </c>
+      <c r="C164" s="5">
+        <f t="shared" si="14"/>
+        <v>341.08387981831368</v>
+      </c>
+      <c r="D164" s="5">
+        <f t="shared" si="15"/>
+        <v>44.466120181686307</v>
+      </c>
+      <c r="E164" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F164" s="5">
+        <f t="shared" si="17"/>
+        <v>22858.630997583237</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <f t="shared" si="12"/>
+        <v>62</v>
+      </c>
+      <c r="B165" s="2">
+        <f t="shared" si="13"/>
+        <v>51014</v>
+      </c>
+      <c r="C165" s="5">
+        <f t="shared" si="14"/>
+        <v>341.73762392129879</v>
+      </c>
+      <c r="D165" s="5">
+        <f t="shared" si="15"/>
+        <v>43.812376078701199</v>
+      </c>
+      <c r="E165" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F165" s="5">
+        <f t="shared" si="17"/>
+        <v>22516.89337366194</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <f t="shared" si="12"/>
+        <v>61</v>
+      </c>
+      <c r="B166" s="2">
+        <f t="shared" si="13"/>
+        <v>51044</v>
+      </c>
+      <c r="C166" s="5">
+        <f t="shared" si="14"/>
+        <v>342.39262103381463</v>
+      </c>
+      <c r="D166" s="5">
+        <f t="shared" si="15"/>
+        <v>43.157378966185384</v>
+      </c>
+      <c r="E166" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F166" s="5">
+        <f t="shared" si="17"/>
+        <v>22174.500752628126</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <f t="shared" si="12"/>
+        <v>60</v>
+      </c>
+      <c r="B167" s="2">
+        <f t="shared" si="13"/>
+        <v>51075</v>
+      </c>
+      <c r="C167" s="5">
+        <f t="shared" si="14"/>
+        <v>343.0488735574628</v>
+      </c>
+      <c r="D167" s="5">
+        <f t="shared" si="15"/>
+        <v>42.501126442537242</v>
+      </c>
+      <c r="E167" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F167" s="5">
+        <f t="shared" si="17"/>
+        <v>21831.451879070664</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+      <c r="B168" s="2">
+        <f t="shared" si="13"/>
+        <v>51105</v>
+      </c>
+      <c r="C168" s="5">
+        <f t="shared" si="14"/>
+        <v>343.70638389844788</v>
+      </c>
+      <c r="D168" s="5">
+        <f t="shared" si="15"/>
+        <v>41.843616101552108</v>
+      </c>
+      <c r="E168" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F168" s="5">
+        <f t="shared" si="17"/>
+        <v>21487.745495172217</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <f t="shared" si="12"/>
+        <v>58</v>
+      </c>
+      <c r="B169" s="2">
+        <f t="shared" si="13"/>
+        <v>51136</v>
+      </c>
+      <c r="C169" s="5">
+        <f t="shared" si="14"/>
+        <v>344.36515446758659</v>
+      </c>
+      <c r="D169" s="5">
+        <f t="shared" si="15"/>
+        <v>41.184845532413412</v>
+      </c>
+      <c r="E169" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F169" s="5">
+        <f t="shared" si="17"/>
+        <v>21143.380340704633</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <f t="shared" si="12"/>
+        <v>57</v>
+      </c>
+      <c r="B170" s="2">
+        <f t="shared" si="13"/>
+        <v>51167</v>
+      </c>
+      <c r="C170" s="5">
+        <f t="shared" si="14"/>
+        <v>345.02518768031615</v>
+      </c>
+      <c r="D170" s="5">
+        <f t="shared" si="15"/>
+        <v>40.524812319683882</v>
+      </c>
+      <c r="E170" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F170" s="5">
+        <f t="shared" si="17"/>
+        <v>20798.355153024317</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <f t="shared" si="12"/>
+        <v>56</v>
+      </c>
+      <c r="B171" s="2">
+        <f t="shared" si="13"/>
+        <v>51196</v>
+      </c>
+      <c r="C171" s="5">
+        <f t="shared" si="14"/>
+        <v>345.68648595670339</v>
+      </c>
+      <c r="D171" s="5">
+        <f t="shared" si="15"/>
+        <v>39.863514043296604</v>
+      </c>
+      <c r="E171" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F171" s="5">
+        <f t="shared" si="17"/>
+        <v>20452.668667067614</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <f t="shared" si="12"/>
+        <v>55</v>
+      </c>
+      <c r="B172" s="2">
+        <f t="shared" si="13"/>
+        <v>51227</v>
+      </c>
+      <c r="C172" s="5">
+        <f t="shared" si="14"/>
+        <v>346.34905172145375</v>
+      </c>
+      <c r="D172" s="5">
+        <f t="shared" si="15"/>
+        <v>39.200948278546257</v>
+      </c>
+      <c r="E172" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F172" s="5">
+        <f t="shared" si="17"/>
+        <v>20106.319615346161</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <f t="shared" si="12"/>
+        <v>54</v>
+      </c>
+      <c r="B173" s="2">
+        <f t="shared" si="13"/>
+        <v>51257</v>
+      </c>
+      <c r="C173" s="5">
+        <f t="shared" si="14"/>
+        <v>347.01288740391988</v>
+      </c>
+      <c r="D173" s="5">
+        <f t="shared" si="15"/>
+        <v>38.537112596080142</v>
+      </c>
+      <c r="E173" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F173" s="5">
+        <f t="shared" si="17"/>
+        <v>19759.306727942243</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <f t="shared" si="12"/>
+        <v>53</v>
+      </c>
+      <c r="B174" s="2">
+        <f t="shared" si="13"/>
+        <v>51288</v>
+      </c>
+      <c r="C174" s="5">
+        <f t="shared" si="14"/>
+        <v>347.67799543811071</v>
+      </c>
+      <c r="D174" s="5">
+        <f t="shared" si="15"/>
+        <v>37.872004561889298</v>
+      </c>
+      <c r="E174" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F174" s="5">
+        <f t="shared" si="17"/>
+        <v>19411.628732504134</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <f t="shared" si="12"/>
+        <v>52</v>
+      </c>
+      <c r="B175" s="2">
+        <f t="shared" si="13"/>
+        <v>51318</v>
+      </c>
+      <c r="C175" s="5">
+        <f t="shared" si="14"/>
+        <v>348.34437826270045</v>
+      </c>
+      <c r="D175" s="5">
+        <f t="shared" si="15"/>
+        <v>37.205621737299587</v>
+      </c>
+      <c r="E175" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F175" s="5">
+        <f t="shared" si="17"/>
+        <v>19063.284354241434</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <f t="shared" si="12"/>
+        <v>51</v>
+      </c>
+      <c r="B176" s="2">
+        <f t="shared" si="13"/>
+        <v>51349</v>
+      </c>
+      <c r="C176" s="5">
+        <f t="shared" si="14"/>
+        <v>349.01203832103727</v>
+      </c>
+      <c r="D176" s="5">
+        <f t="shared" si="15"/>
+        <v>36.537961678962752</v>
+      </c>
+      <c r="E176" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F176" s="5">
+        <f t="shared" si="17"/>
+        <v>18714.272315920396</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <f t="shared" si="12"/>
+        <v>50</v>
+      </c>
+      <c r="B177" s="2">
+        <f t="shared" si="13"/>
+        <v>51380</v>
+      </c>
+      <c r="C177" s="5">
+        <f t="shared" si="14"/>
+        <v>349.68097806115259</v>
+      </c>
+      <c r="D177" s="5">
+        <f t="shared" si="15"/>
+        <v>35.869021938847425</v>
+      </c>
+      <c r="E177" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F177" s="5">
+        <f t="shared" si="17"/>
+        <v>18364.591337859245</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <f t="shared" si="12"/>
+        <v>49</v>
+      </c>
+      <c r="B178" s="2">
+        <f t="shared" si="13"/>
+        <v>51410</v>
+      </c>
+      <c r="C178" s="5">
+        <f t="shared" si="14"/>
+        <v>350.35119993576978</v>
+      </c>
+      <c r="D178" s="5">
+        <f t="shared" si="15"/>
+        <v>35.19880006423022</v>
+      </c>
+      <c r="E178" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F178" s="5">
+        <f t="shared" si="17"/>
+        <v>18014.240137923476</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+      <c r="B179" s="2">
+        <f t="shared" si="13"/>
+        <v>51441</v>
+      </c>
+      <c r="C179" s="5">
+        <f t="shared" si="14"/>
+        <v>351.02270640231336</v>
+      </c>
+      <c r="D179" s="5">
+        <f t="shared" si="15"/>
+        <v>34.527293597686658</v>
+      </c>
+      <c r="E179" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F179" s="5">
+        <f t="shared" si="17"/>
+        <v>17663.217431521163</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <f t="shared" si="12"/>
+        <v>47</v>
+      </c>
+      <c r="B180" s="2">
+        <f t="shared" si="13"/>
+        <v>51471</v>
+      </c>
+      <c r="C180" s="5">
+        <f t="shared" si="14"/>
+        <v>351.6954999229178</v>
+      </c>
+      <c r="D180" s="5">
+        <f t="shared" si="15"/>
+        <v>33.854500077082228</v>
+      </c>
+      <c r="E180" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F180" s="5">
+        <f t="shared" si="17"/>
+        <v>17311.521931598247</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <f t="shared" si="12"/>
+        <v>46</v>
+      </c>
+      <c r="B181" s="2">
+        <f t="shared" si="13"/>
+        <v>51502</v>
+      </c>
+      <c r="C181" s="5">
+        <f t="shared" si="14"/>
+        <v>352.36958296443669</v>
+      </c>
+      <c r="D181" s="5">
+        <f t="shared" si="15"/>
+        <v>33.180417035563302</v>
+      </c>
+      <c r="E181" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F181" s="5">
+        <f t="shared" si="17"/>
+        <v>16959.152348633808</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <f t="shared" si="12"/>
+        <v>45</v>
+      </c>
+      <c r="B182" s="2">
+        <f t="shared" si="13"/>
+        <v>51533</v>
+      </c>
+      <c r="C182" s="5">
+        <f t="shared" si="14"/>
+        <v>353.04495799845188</v>
+      </c>
+      <c r="D182" s="5">
+        <f t="shared" si="15"/>
+        <v>32.505042001548134</v>
+      </c>
+      <c r="E182" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F182" s="5">
+        <f t="shared" si="17"/>
+        <v>16606.107390635356</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="B183" s="2">
+        <f t="shared" si="13"/>
+        <v>51561</v>
+      </c>
+      <c r="C183" s="5">
+        <f t="shared" si="14"/>
+        <v>353.72162750128223</v>
+      </c>
+      <c r="D183" s="5">
+        <f t="shared" si="15"/>
+        <v>31.828372498717766</v>
+      </c>
+      <c r="E183" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F183" s="5">
+        <f t="shared" si="17"/>
+        <v>16252.385763134074</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <f t="shared" si="12"/>
+        <v>43</v>
+      </c>
+      <c r="B184" s="2">
+        <f t="shared" si="13"/>
+        <v>51592</v>
+      </c>
+      <c r="C184" s="5">
+        <f t="shared" si="14"/>
+        <v>354.39959395399302</v>
+      </c>
+      <c r="D184" s="5">
+        <f t="shared" si="15"/>
+        <v>31.150406046006974</v>
+      </c>
+      <c r="E184" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F184" s="5">
+        <f t="shared" si="17"/>
+        <v>15897.986169180082</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <f t="shared" si="12"/>
+        <v>42</v>
+      </c>
+      <c r="B185" s="2">
+        <f t="shared" si="13"/>
+        <v>51622</v>
+      </c>
+      <c r="C185" s="5">
+        <f t="shared" si="14"/>
+        <v>355.07885984240488</v>
+      </c>
+      <c r="D185" s="5">
+        <f t="shared" si="15"/>
+        <v>30.471140157595155</v>
+      </c>
+      <c r="E185" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F185" s="5">
+        <f t="shared" si="17"/>
+        <v>15542.907309337677</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <f t="shared" si="12"/>
+        <v>41</v>
+      </c>
+      <c r="B186" s="2">
+        <f t="shared" si="13"/>
+        <v>51653</v>
+      </c>
+      <c r="C186" s="5">
+        <f t="shared" si="14"/>
+        <v>355.75942765710278</v>
+      </c>
+      <c r="D186" s="5">
+        <f t="shared" si="15"/>
+        <v>29.790572342897217</v>
+      </c>
+      <c r="E186" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F186" s="5">
+        <f t="shared" si="17"/>
+        <v>15187.147881680574</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="B187" s="2">
+        <f t="shared" si="13"/>
+        <v>51683</v>
+      </c>
+      <c r="C187" s="5">
+        <f t="shared" si="14"/>
+        <v>356.4412998934456</v>
+      </c>
+      <c r="D187" s="5">
+        <f t="shared" si="15"/>
+        <v>29.108700106554434</v>
+      </c>
+      <c r="E187" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F187" s="5">
+        <f t="shared" si="17"/>
+        <v>14830.706581787128</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <f t="shared" si="12"/>
+        <v>39</v>
+      </c>
+      <c r="B188" s="2">
+        <f t="shared" si="13"/>
+        <v>51714</v>
+      </c>
+      <c r="C188" s="5">
+        <f t="shared" si="14"/>
+        <v>357.12447905157467</v>
+      </c>
+      <c r="D188" s="5">
+        <f t="shared" si="15"/>
+        <v>28.42552094842533</v>
+      </c>
+      <c r="E188" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F188" s="5">
+        <f t="shared" si="17"/>
+        <v>14473.582102735554</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <f t="shared" si="12"/>
+        <v>38</v>
+      </c>
+      <c r="B189" s="2">
+        <f t="shared" si="13"/>
+        <v>51745</v>
+      </c>
+      <c r="C189" s="5">
+        <f t="shared" si="14"/>
+        <v>357.80896763642352</v>
+      </c>
+      <c r="D189" s="5">
+        <f t="shared" si="15"/>
+        <v>27.74103236357648</v>
+      </c>
+      <c r="E189" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F189" s="5">
+        <f t="shared" si="17"/>
+        <v>14115.773135099131</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <f t="shared" si="12"/>
+        <v>37</v>
+      </c>
+      <c r="B190" s="2">
+        <f t="shared" si="13"/>
+        <v>51775</v>
+      </c>
+      <c r="C190" s="5">
+        <f t="shared" si="14"/>
+        <v>358.4947681577267</v>
+      </c>
+      <c r="D190" s="5">
+        <f t="shared" si="15"/>
+        <v>27.055231842273333</v>
+      </c>
+      <c r="E190" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F190" s="5">
+        <f t="shared" si="17"/>
+        <v>13757.278366941404</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <f t="shared" si="12"/>
+        <v>36</v>
+      </c>
+      <c r="B191" s="2">
+        <f t="shared" si="13"/>
+        <v>51806</v>
+      </c>
+      <c r="C191" s="5">
+        <f t="shared" si="14"/>
+        <v>359.18188313002901</v>
+      </c>
+      <c r="D191" s="5">
+        <f t="shared" si="15"/>
+        <v>26.368116869971022</v>
+      </c>
+      <c r="E191" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F191" s="5">
+        <f t="shared" si="17"/>
+        <v>13398.096483811374</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <f t="shared" si="12"/>
+        <v>35</v>
+      </c>
+      <c r="B192" s="2">
+        <f t="shared" si="13"/>
+        <v>51836</v>
+      </c>
+      <c r="C192" s="5">
+        <f t="shared" si="14"/>
+        <v>359.87031507269489</v>
+      </c>
+      <c r="D192" s="5">
+        <f t="shared" si="15"/>
+        <v>25.679684927305132</v>
+      </c>
+      <c r="E192" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F192" s="5">
+        <f t="shared" si="17"/>
+        <v>13038.22616873868</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <f t="shared" si="12"/>
+        <v>34</v>
+      </c>
+      <c r="B193" s="2">
+        <f t="shared" si="13"/>
+        <v>51867</v>
+      </c>
+      <c r="C193" s="5">
+        <f t="shared" si="14"/>
+        <v>360.56006650991753</v>
+      </c>
+      <c r="D193" s="5">
+        <f t="shared" si="15"/>
+        <v>24.989933490082468</v>
+      </c>
+      <c r="E193" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F193" s="5">
+        <f t="shared" si="17"/>
+        <v>12677.666102228763</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <f t="shared" si="12"/>
+        <v>33</v>
+      </c>
+      <c r="B194" s="2">
+        <f t="shared" si="13"/>
+        <v>51898</v>
+      </c>
+      <c r="C194" s="5">
+        <f t="shared" si="14"/>
+        <v>361.25113997072822</v>
+      </c>
+      <c r="D194" s="5">
+        <f t="shared" si="15"/>
+        <v>24.298860029271793</v>
+      </c>
+      <c r="E194" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F194" s="5">
+        <f t="shared" si="17"/>
+        <v>12316.414962258033</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <f t="shared" si="12"/>
+        <v>32</v>
+      </c>
+      <c r="B195" s="2">
+        <f t="shared" si="13"/>
+        <v>51926</v>
+      </c>
+      <c r="C195" s="5">
+        <f t="shared" si="14"/>
+        <v>361.94353798900545</v>
+      </c>
+      <c r="D195" s="5">
+        <f t="shared" si="15"/>
+        <v>23.606462010994562</v>
+      </c>
+      <c r="E195" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F195" s="5">
+        <f t="shared" si="17"/>
+        <v>11954.471424269028</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <f t="shared" si="12"/>
+        <v>31</v>
+      </c>
+      <c r="B196" s="2">
+        <f t="shared" si="13"/>
+        <v>51957</v>
+      </c>
+      <c r="C196" s="5">
+        <f t="shared" si="14"/>
+        <v>362.63726310348437</v>
+      </c>
+      <c r="D196" s="5">
+        <f t="shared" si="15"/>
+        <v>22.912736896515636</v>
+      </c>
+      <c r="E196" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F196" s="5">
+        <f t="shared" si="17"/>
+        <v>11591.834161165543</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="B197" s="2">
+        <f t="shared" si="13"/>
+        <v>51987</v>
+      </c>
+      <c r="C197" s="5">
+        <f t="shared" si="14"/>
+        <v>363.33231785776604</v>
+      </c>
+      <c r="D197" s="5">
+        <f t="shared" si="15"/>
+        <v>22.217682142233958</v>
+      </c>
+      <c r="E197" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F197" s="5">
+        <f t="shared" si="17"/>
+        <v>11228.501843307777</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="B198" s="2">
+        <f t="shared" si="13"/>
+        <v>52018</v>
+      </c>
+      <c r="C198" s="5">
+        <f t="shared" si="14"/>
+        <v>364.02870480032675</v>
+      </c>
+      <c r="D198" s="5">
+        <f t="shared" si="15"/>
+        <v>21.521295199673236</v>
+      </c>
+      <c r="E198" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F198" s="5">
+        <f t="shared" si="17"/>
+        <v>10864.47313850745</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="B199" s="2">
+        <f t="shared" si="13"/>
+        <v>52048</v>
+      </c>
+      <c r="C199" s="5">
+        <f t="shared" si="14"/>
+        <v>364.72642648452739</v>
+      </c>
+      <c r="D199" s="5">
+        <f t="shared" si="15"/>
+        <v>20.823573515472614</v>
+      </c>
+      <c r="E199" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F199" s="5">
+        <f t="shared" si="17"/>
+        <v>10499.746712022923</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="B200" s="2">
+        <f t="shared" si="13"/>
+        <v>52079</v>
+      </c>
+      <c r="C200" s="5">
+        <f t="shared" si="14"/>
+        <v>365.42548546862275</v>
+      </c>
+      <c r="D200" s="5">
+        <f t="shared" si="15"/>
+        <v>20.124514531377269</v>
+      </c>
+      <c r="E200" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F200" s="5">
+        <f t="shared" si="17"/>
+        <v>10134.321226554301</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <f t="shared" ref="A201:A226" si="18">A200-1</f>
+        <v>26</v>
+      </c>
+      <c r="B201" s="2">
+        <f t="shared" si="13"/>
+        <v>52110</v>
+      </c>
+      <c r="C201" s="5">
+        <f t="shared" si="14"/>
+        <v>366.12588431577092</v>
+      </c>
+      <c r="D201" s="5">
+        <f t="shared" si="15"/>
+        <v>19.424115684229076</v>
+      </c>
+      <c r="E201" s="5">
+        <f t="shared" si="16"/>
+        <v>385.55</v>
+      </c>
+      <c r="F201" s="5">
+        <f t="shared" si="17"/>
+        <v>9768.1953422385304</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <f t="shared" si="18"/>
+        <v>25</v>
+      </c>
+      <c r="B202" s="2">
+        <f t="shared" ref="B202:B226" si="19">EDATE(B201,1)</f>
+        <v>52140</v>
+      </c>
+      <c r="C202" s="5">
+        <f t="shared" ref="C202:C226" si="20">$C$2-D202</f>
+        <v>366.82762559404284</v>
+      </c>
+      <c r="D202" s="5">
+        <f t="shared" ref="D202:D226" si="21">F201*$B$2/12</f>
+        <v>18.722374405957183</v>
+      </c>
+      <c r="E202" s="5">
+        <f t="shared" ref="E202:E226" si="22">$C$2</f>
+        <v>385.55</v>
+      </c>
+      <c r="F202" s="5">
+        <f t="shared" ref="F202:F226" si="23">F201-C202</f>
+        <v>9401.3677166444868</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <f t="shared" si="18"/>
+        <v>24</v>
+      </c>
+      <c r="B203" s="2">
+        <f t="shared" si="19"/>
+        <v>52171</v>
+      </c>
+      <c r="C203" s="5">
+        <f t="shared" si="20"/>
+        <v>367.53071187643138</v>
+      </c>
+      <c r="D203" s="5">
+        <f t="shared" si="21"/>
+        <v>18.0192881235686</v>
+      </c>
+      <c r="E203" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F203" s="5">
+        <f t="shared" si="23"/>
+        <v>9033.8370047680546</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <f t="shared" si="18"/>
+        <v>23</v>
+      </c>
+      <c r="B204" s="2">
+        <f t="shared" si="19"/>
+        <v>52201</v>
+      </c>
+      <c r="C204" s="5">
+        <f t="shared" si="20"/>
+        <v>368.23514574086124</v>
+      </c>
+      <c r="D204" s="5">
+        <f t="shared" si="21"/>
+        <v>17.314854259138773</v>
+      </c>
+      <c r="E204" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F204" s="5">
+        <f t="shared" si="23"/>
+        <v>8665.6018590271942</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <f t="shared" si="18"/>
+        <v>22</v>
+      </c>
+      <c r="B205" s="2">
+        <f t="shared" si="19"/>
+        <v>52232</v>
+      </c>
+      <c r="C205" s="5">
+        <f t="shared" si="20"/>
+        <v>368.9409297701979</v>
+      </c>
+      <c r="D205" s="5">
+        <f t="shared" si="21"/>
+        <v>16.609070229802121</v>
+      </c>
+      <c r="E205" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F205" s="5">
+        <f t="shared" si="23"/>
+        <v>8296.6609292569956</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <f t="shared" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="B206" s="2">
+        <f t="shared" si="19"/>
+        <v>52263</v>
+      </c>
+      <c r="C206" s="5">
+        <f t="shared" si="20"/>
+        <v>369.64806655225743</v>
+      </c>
+      <c r="D206" s="5">
+        <f t="shared" si="21"/>
+        <v>15.901933447742573</v>
+      </c>
+      <c r="E206" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F206" s="5">
+        <f t="shared" si="23"/>
+        <v>7927.0128627047379</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <f t="shared" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="B207" s="2">
+        <f t="shared" si="19"/>
+        <v>52291</v>
+      </c>
+      <c r="C207" s="5">
+        <f t="shared" si="20"/>
+        <v>370.35655867981592</v>
+      </c>
+      <c r="D207" s="5">
+        <f t="shared" si="21"/>
+        <v>15.19344132018408</v>
+      </c>
+      <c r="E207" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F207" s="5">
+        <f t="shared" si="23"/>
+        <v>7556.6563040249221</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <f t="shared" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="B208" s="2">
+        <f t="shared" si="19"/>
+        <v>52322</v>
+      </c>
+      <c r="C208" s="5">
+        <f t="shared" si="20"/>
+        <v>371.0664087506189</v>
+      </c>
+      <c r="D208" s="5">
+        <f t="shared" si="21"/>
+        <v>14.483591249381099</v>
+      </c>
+      <c r="E208" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F208" s="5">
+        <f t="shared" si="23"/>
+        <v>7185.5898952743028</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <f t="shared" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="B209" s="2">
+        <f t="shared" si="19"/>
+        <v>52352</v>
+      </c>
+      <c r="C209" s="5">
+        <f t="shared" si="20"/>
+        <v>371.77761936739091</v>
+      </c>
+      <c r="D209" s="5">
+        <f t="shared" si="21"/>
+        <v>13.77238063260908</v>
+      </c>
+      <c r="E209" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F209" s="5">
+        <f t="shared" si="23"/>
+        <v>6813.812275906912</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <f t="shared" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="B210" s="2">
+        <f t="shared" si="19"/>
+        <v>52383</v>
+      </c>
+      <c r="C210" s="5">
+        <f t="shared" si="20"/>
+        <v>372.4901931378451</v>
+      </c>
+      <c r="D210" s="5">
+        <f t="shared" si="21"/>
+        <v>13.059806862154915</v>
+      </c>
+      <c r="E210" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F210" s="5">
+        <f t="shared" si="23"/>
+        <v>6441.3220827690666</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <f t="shared" si="18"/>
+        <v>16</v>
+      </c>
+      <c r="B211" s="2">
+        <f t="shared" si="19"/>
+        <v>52413</v>
+      </c>
+      <c r="C211" s="5">
+        <f t="shared" si="20"/>
+        <v>373.20413267469263</v>
+      </c>
+      <c r="D211" s="5">
+        <f t="shared" si="21"/>
+        <v>12.345867325307376</v>
+      </c>
+      <c r="E211" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F211" s="5">
+        <f t="shared" si="23"/>
+        <v>6068.1179500943736</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <f t="shared" si="18"/>
+        <v>15</v>
+      </c>
+      <c r="B212" s="2">
+        <f t="shared" si="19"/>
+        <v>52444</v>
+      </c>
+      <c r="C212" s="5">
+        <f t="shared" si="20"/>
+        <v>373.91944059565247</v>
+      </c>
+      <c r="D212" s="5">
+        <f t="shared" si="21"/>
+        <v>11.630559404347549</v>
+      </c>
+      <c r="E212" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F212" s="5">
+        <f t="shared" si="23"/>
+        <v>5694.1985094987213</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <f t="shared" si="18"/>
+        <v>14</v>
+      </c>
+      <c r="B213" s="2">
+        <f t="shared" si="19"/>
+        <v>52475</v>
+      </c>
+      <c r="C213" s="5">
+        <f t="shared" si="20"/>
+        <v>374.63611952346082</v>
+      </c>
+      <c r="D213" s="5">
+        <f t="shared" si="21"/>
+        <v>10.913880476539214</v>
+      </c>
+      <c r="E213" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F213" s="5">
+        <f t="shared" si="23"/>
+        <v>5319.5623899752609</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <f t="shared" si="18"/>
+        <v>13</v>
+      </c>
+      <c r="B214" s="2">
+        <f t="shared" si="19"/>
+        <v>52505</v>
+      </c>
+      <c r="C214" s="5">
+        <f t="shared" si="20"/>
+        <v>375.35417208588075</v>
+      </c>
+      <c r="D214" s="5">
+        <f t="shared" si="21"/>
+        <v>10.195827914119251</v>
+      </c>
+      <c r="E214" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F214" s="5">
+        <f t="shared" si="23"/>
+        <v>4944.2082178893797</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <f t="shared" si="18"/>
+        <v>12</v>
+      </c>
+      <c r="B215" s="2">
+        <f t="shared" si="19"/>
+        <v>52536</v>
+      </c>
+      <c r="C215" s="5">
+        <f t="shared" si="20"/>
+        <v>376.07360091571201</v>
+      </c>
+      <c r="D215" s="5">
+        <f t="shared" si="21"/>
+        <v>9.4763990842879782</v>
+      </c>
+      <c r="E215" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F215" s="5">
+        <f t="shared" si="23"/>
+        <v>4568.134616973668</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="B216" s="2">
+        <f t="shared" si="19"/>
+        <v>52566</v>
+      </c>
+      <c r="C216" s="5">
+        <f t="shared" si="20"/>
+        <v>376.79440865080051</v>
+      </c>
+      <c r="D216" s="5">
+        <f t="shared" si="21"/>
+        <v>8.7555913491995305</v>
+      </c>
+      <c r="E216" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F216" s="5">
+        <f t="shared" si="23"/>
+        <v>4191.3402083228675</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="B217" s="2">
+        <f t="shared" si="19"/>
+        <v>52597</v>
+      </c>
+      <c r="C217" s="5">
+        <f t="shared" si="20"/>
+        <v>377.51659793404787</v>
+      </c>
+      <c r="D217" s="5">
+        <f t="shared" si="21"/>
+        <v>8.0334020659521617</v>
+      </c>
+      <c r="E217" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F217" s="5">
+        <f t="shared" si="23"/>
+        <v>3813.8236103888198</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="B218" s="2">
+        <f t="shared" si="19"/>
+        <v>52628</v>
+      </c>
+      <c r="C218" s="5">
+        <f t="shared" si="20"/>
+        <v>378.24017141342142</v>
+      </c>
+      <c r="D218" s="5">
+        <f t="shared" si="21"/>
+        <v>7.309828586578571</v>
+      </c>
+      <c r="E218" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F218" s="5">
+        <f t="shared" si="23"/>
+        <v>3435.5834389753982</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <f t="shared" si="18"/>
+        <v>8</v>
+      </c>
+      <c r="B219" s="2">
+        <f t="shared" si="19"/>
+        <v>52657</v>
+      </c>
+      <c r="C219" s="5">
+        <f t="shared" si="20"/>
+        <v>378.96513174196383</v>
+      </c>
+      <c r="D219" s="5">
+        <f t="shared" si="21"/>
+        <v>6.5848682580361801</v>
+      </c>
+      <c r="E219" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F219" s="5">
+        <f t="shared" si="23"/>
+        <v>3056.6183072334343</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="B220" s="2">
+        <f t="shared" si="19"/>
+        <v>52688</v>
+      </c>
+      <c r="C220" s="5">
+        <f t="shared" si="20"/>
+        <v>379.69148157780262</v>
+      </c>
+      <c r="D220" s="5">
+        <f t="shared" si="21"/>
+        <v>5.8585184221974158</v>
+      </c>
+      <c r="E220" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F220" s="5">
+        <f t="shared" si="23"/>
+        <v>2676.9268256556315</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+      <c r="B221" s="2">
+        <f t="shared" si="19"/>
+        <v>52718</v>
+      </c>
+      <c r="C221" s="5">
+        <f t="shared" si="20"/>
+        <v>380.41922358416008</v>
+      </c>
+      <c r="D221" s="5">
+        <f t="shared" si="21"/>
+        <v>5.1307764158399598</v>
+      </c>
+      <c r="E221" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F221" s="5">
+        <f t="shared" si="23"/>
+        <v>2296.5076020714714</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="B222" s="2">
+        <f t="shared" si="19"/>
+        <v>52749</v>
+      </c>
+      <c r="C222" s="5">
+        <f t="shared" si="20"/>
+        <v>381.14836042936304</v>
+      </c>
+      <c r="D222" s="5">
+        <f t="shared" si="21"/>
+        <v>4.4016395706369869</v>
+      </c>
+      <c r="E222" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F222" s="5">
+        <f t="shared" si="23"/>
+        <v>1915.3592416421084</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="B223" s="2">
+        <f t="shared" si="19"/>
+        <v>52779</v>
+      </c>
+      <c r="C223" s="5">
+        <f t="shared" si="20"/>
+        <v>381.87889478685264</v>
+      </c>
+      <c r="D223" s="5">
+        <f t="shared" si="21"/>
+        <v>3.6711052131473743</v>
+      </c>
+      <c r="E223" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F223" s="5">
+        <f t="shared" si="23"/>
+        <v>1533.4803468552557</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <f t="shared" si="18"/>
+        <v>3</v>
+      </c>
+      <c r="B224" s="2">
+        <f t="shared" si="19"/>
+        <v>52810</v>
+      </c>
+      <c r="C224" s="5">
+        <f t="shared" si="20"/>
+        <v>382.61082933519413</v>
+      </c>
+      <c r="D224" s="5">
+        <f t="shared" si="21"/>
+        <v>2.9391706648059066</v>
+      </c>
+      <c r="E224" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F224" s="5">
+        <f t="shared" si="23"/>
+        <v>1150.8695175200614</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="B225" s="2">
+        <f t="shared" si="19"/>
+        <v>52841</v>
+      </c>
+      <c r="C225" s="5">
+        <f t="shared" si="20"/>
+        <v>383.34416675808654</v>
+      </c>
+      <c r="D225" s="5">
+        <f t="shared" si="21"/>
+        <v>2.2058332419134508</v>
+      </c>
+      <c r="E225" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F225" s="5">
+        <f t="shared" si="23"/>
+        <v>767.52535076197489</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="B226" s="2">
+        <f t="shared" si="19"/>
+        <v>52871</v>
+      </c>
+      <c r="C226" s="5">
+        <f t="shared" si="20"/>
+        <v>384.07890974437288</v>
+      </c>
+      <c r="D226" s="5">
+        <f t="shared" si="21"/>
+        <v>1.4710902556271186</v>
+      </c>
+      <c r="E226" s="5">
+        <f t="shared" si="22"/>
+        <v>385.55</v>
+      </c>
+      <c r="F226" s="5">
+        <f t="shared" si="23"/>
+        <v>383.44644101760201</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E228" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E229" s="5">
+        <f>SUM(E5:E226)</f>
+        <v>115340.94000000061</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>